--- a/research/traditional_assets/database/data/malaysia/malaysia_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_precious_metals.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1071955603824255</v>
+        <v>0.1069724910375077</v>
       </c>
       <c r="C2">
-        <v>328.5230322520903</v>
+        <v>326.3598576571492</v>
       </c>
       <c r="D2">
-        <v>308.0230322520903</v>
+        <v>309.1462576571492</v>
       </c>
       <c r="E2">
-        <v>-2.74</v>
+        <v>0.5463999999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.2864</v>
       </c>
       <c r="G2">
         <v>20.5</v>
@@ -1433,28 +1433,28 @@
         <v>11.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.16530592</v>
       </c>
       <c r="N2">
-        <v>11.3</v>
+        <v>11.13469408</v>
       </c>
       <c r="O2">
-        <v>2.712</v>
+        <v>2.6723265792</v>
       </c>
       <c r="P2">
-        <v>8.588000000000001</v>
+        <v>8.462367500800001</v>
       </c>
       <c r="Q2">
-        <v>12.588</v>
+        <v>12.4623675008</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1071955603824255</v>
+        <v>0.1076668798358663</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.043164473329153</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>68.35810840894266</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1069724910375077</v>
+        <v>0.1067494216925898</v>
       </c>
       <c r="C3">
-        <v>326.3598576571492</v>
+        <v>324.2049048680383</v>
       </c>
       <c r="D3">
-        <v>309.1462576571492</v>
+        <v>310.2777048680383</v>
       </c>
       <c r="E3">
-        <v>0.5463999999999998</v>
+        <v>3.8328</v>
       </c>
       <c r="F3">
-        <v>3.2864</v>
+        <v>6.5728</v>
       </c>
       <c r="G3">
         <v>20.5</v>
@@ -1515,28 +1515,28 @@
         <v>11.3</v>
       </c>
       <c r="M3">
-        <v>0.16530592</v>
+        <v>0.33061184</v>
       </c>
       <c r="N3">
-        <v>11.13469408</v>
+        <v>10.96938816</v>
       </c>
       <c r="O3">
-        <v>2.6723265792</v>
+        <v>2.6326531584</v>
       </c>
       <c r="P3">
-        <v>8.462367500800001</v>
+        <v>8.336735001600001</v>
       </c>
       <c r="Q3">
-        <v>12.4623675008</v>
+        <v>12.3367350016</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1076668798358663</v>
+        <v>0.1081478180536631</v>
       </c>
       <c r="T3">
-        <v>1.043164473329153</v>
+        <v>1.051273782607443</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>68.35810840894266</v>
+        <v>34.17905420447133</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1067494216925898</v>
+        <v>0.106526352347672</v>
       </c>
       <c r="C4">
-        <v>324.2049048680383</v>
+        <v>322.0582644895492</v>
       </c>
       <c r="D4">
-        <v>310.2777048680383</v>
+        <v>311.4174644895492</v>
       </c>
       <c r="E4">
-        <v>3.8328</v>
+        <v>7.119199999999999</v>
       </c>
       <c r="F4">
-        <v>6.5728</v>
+        <v>9.8592</v>
       </c>
       <c r="G4">
         <v>20.5</v>
@@ -1597,28 +1597,28 @@
         <v>11.3</v>
       </c>
       <c r="M4">
-        <v>0.33061184</v>
+        <v>0.4959177599999999</v>
       </c>
       <c r="N4">
-        <v>10.96938816</v>
+        <v>10.80408224</v>
       </c>
       <c r="O4">
-        <v>2.6326531584</v>
+        <v>2.5929797376</v>
       </c>
       <c r="P4">
-        <v>8.336735001600001</v>
+        <v>8.211102502400001</v>
       </c>
       <c r="Q4">
-        <v>12.3367350016</v>
+        <v>12.2111025024</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1081478180536631</v>
+        <v>0.1086386725233732</v>
       </c>
       <c r="T4">
-        <v>1.051273782607443</v>
+        <v>1.059550294138894</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.17905420447133</v>
+        <v>22.78603613631422</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.106526352347672</v>
+        <v>0.1063032830027542</v>
       </c>
       <c r="C5">
-        <v>322.0582644895492</v>
+        <v>319.9200284626759</v>
       </c>
       <c r="D5">
-        <v>311.4174644895492</v>
+        <v>312.5656284626759</v>
       </c>
       <c r="E5">
-        <v>7.119199999999999</v>
+        <v>10.4056</v>
       </c>
       <c r="F5">
-        <v>9.8592</v>
+        <v>13.1456</v>
       </c>
       <c r="G5">
         <v>20.5</v>
@@ -1679,28 +1679,28 @@
         <v>11.3</v>
       </c>
       <c r="M5">
-        <v>0.4959177599999999</v>
+        <v>0.66122368</v>
       </c>
       <c r="N5">
-        <v>10.80408224</v>
+        <v>10.63877632</v>
       </c>
       <c r="O5">
-        <v>2.5929797376</v>
+        <v>2.5533063168</v>
       </c>
       <c r="P5">
-        <v>8.211102502400001</v>
+        <v>8.085470003200001</v>
       </c>
       <c r="Q5">
-        <v>12.2111025024</v>
+        <v>12.0854700032</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1086386725233732</v>
+        <v>0.109139753127869</v>
       </c>
       <c r="T5">
-        <v>1.059550294138894</v>
+        <v>1.067999232993916</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.78603613631422</v>
+        <v>17.08952710223566</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1063032830027542</v>
+        <v>0.1060802136578364</v>
       </c>
       <c r="C6">
-        <v>319.9200284626759</v>
+        <v>317.7902900893378</v>
       </c>
       <c r="D6">
-        <v>312.5656284626759</v>
+        <v>313.7222900893378</v>
       </c>
       <c r="E6">
-        <v>10.4056</v>
+        <v>13.692</v>
       </c>
       <c r="F6">
-        <v>13.1456</v>
+        <v>16.432</v>
       </c>
       <c r="G6">
         <v>20.5</v>
@@ -1761,28 +1761,28 @@
         <v>11.3</v>
       </c>
       <c r="M6">
-        <v>0.66122368</v>
+        <v>0.8265295999999999</v>
       </c>
       <c r="N6">
-        <v>10.63877632</v>
+        <v>10.4734704</v>
       </c>
       <c r="O6">
-        <v>2.5533063168</v>
+        <v>2.513632896</v>
       </c>
       <c r="P6">
-        <v>8.085470003200001</v>
+        <v>7.959837504</v>
       </c>
       <c r="Q6">
-        <v>12.0854700032</v>
+        <v>11.959837504</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.109139753127869</v>
+        <v>0.1096513827977225</v>
       </c>
       <c r="T6">
-        <v>1.067999232993916</v>
+        <v>1.076626044245886</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.08952710223566</v>
+        <v>13.67162168178853</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1060802136578364</v>
+        <v>0.1059255443129186</v>
       </c>
       <c r="C7">
-        <v>317.7902900893378</v>
+        <v>315.3109218035407</v>
       </c>
       <c r="D7">
-        <v>313.7222900893378</v>
+        <v>314.5293218035407</v>
       </c>
       <c r="E7">
-        <v>13.692</v>
+        <v>16.9784</v>
       </c>
       <c r="F7">
-        <v>16.432</v>
+        <v>19.7184</v>
       </c>
       <c r="G7">
         <v>20.5</v>
@@ -1843,45 +1843,45 @@
         <v>11.3</v>
       </c>
       <c r="M7">
-        <v>0.8265295999999999</v>
+        <v>1.02141312</v>
       </c>
       <c r="N7">
-        <v>10.4734704</v>
+        <v>10.27858688</v>
       </c>
       <c r="O7">
-        <v>2.513632896</v>
+        <v>2.4668608512</v>
       </c>
       <c r="P7">
-        <v>7.959837504</v>
+        <v>7.811726028800001</v>
       </c>
       <c r="Q7">
-        <v>11.959837504</v>
+        <v>11.8117260288</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1096513827977225</v>
+        <v>0.1101738982052325</v>
       </c>
       <c r="T7">
-        <v>1.076626044245886</v>
+        <v>1.08543640467343</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.67162168178853</v>
+        <v>11.0631044175348</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1059255443129186</v>
+        <v>0.1058043149680007</v>
       </c>
       <c r="C8">
-        <v>315.3109218035407</v>
+        <v>312.6599791645658</v>
       </c>
       <c r="D8">
-        <v>314.5293218035407</v>
+        <v>315.1647791645658</v>
       </c>
       <c r="E8">
-        <v>16.9784</v>
+        <v>20.26479999999999</v>
       </c>
       <c r="F8">
-        <v>19.7184</v>
+        <v>23.0048</v>
       </c>
       <c r="G8">
         <v>20.5</v>
@@ -1925,45 +1925,45 @@
         <v>11.3</v>
       </c>
       <c r="M8">
-        <v>1.02141312</v>
+        <v>1.2307568</v>
       </c>
       <c r="N8">
-        <v>10.27858688</v>
+        <v>10.0692432</v>
       </c>
       <c r="O8">
-        <v>2.4668608512</v>
+        <v>2.416618368</v>
       </c>
       <c r="P8">
-        <v>7.811726028800001</v>
+        <v>7.652624832000001</v>
       </c>
       <c r="Q8">
-        <v>11.8117260288</v>
+        <v>11.652624832</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1101738982052325</v>
+        <v>0.1107076505032266</v>
       </c>
       <c r="T8">
-        <v>1.08543640467343</v>
+        <v>1.094436235217696</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.0631044175348</v>
+        <v>9.181342731561591</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1058043149680007</v>
+        <v>0.1056055656230829</v>
       </c>
       <c r="C9">
-        <v>312.6599791645658</v>
+        <v>310.4209531463604</v>
       </c>
       <c r="D9">
-        <v>315.1647791645658</v>
+        <v>316.2121531463604</v>
       </c>
       <c r="E9">
-        <v>20.2648</v>
+        <v>23.5512</v>
       </c>
       <c r="F9">
-        <v>23.0048</v>
+        <v>26.2912</v>
       </c>
       <c r="G9">
         <v>20.5</v>
@@ -2007,28 +2007,28 @@
         <v>11.3</v>
       </c>
       <c r="M9">
-        <v>1.2307568</v>
+        <v>1.4065792</v>
       </c>
       <c r="N9">
-        <v>10.0692432</v>
+        <v>9.893420800000001</v>
       </c>
       <c r="O9">
-        <v>2.416618368</v>
+        <v>2.374420992</v>
       </c>
       <c r="P9">
-        <v>7.652624832000001</v>
+        <v>7.518999808000001</v>
       </c>
       <c r="Q9">
-        <v>11.652624832</v>
+        <v>11.518999808</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1107076505032266</v>
+        <v>0.1112530061120466</v>
       </c>
       <c r="T9">
-        <v>1.094436235217696</v>
+        <v>1.103631714252054</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.181342731561589</v>
+        <v>8.033674890116391</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1056055656230829</v>
+        <v>0.1054615362781651</v>
       </c>
       <c r="C10">
-        <v>310.4209531463604</v>
+        <v>307.8979231853145</v>
       </c>
       <c r="D10">
-        <v>316.2121531463604</v>
+        <v>316.9755231853145</v>
       </c>
       <c r="E10">
-        <v>23.5512</v>
+        <v>26.83759999999999</v>
       </c>
       <c r="F10">
-        <v>26.2912</v>
+        <v>29.5776</v>
       </c>
       <c r="G10">
         <v>20.5</v>
@@ -2089,45 +2089,45 @@
         <v>11.3</v>
       </c>
       <c r="M10">
-        <v>1.4065792</v>
+        <v>1.60606368</v>
       </c>
       <c r="N10">
-        <v>9.893420800000001</v>
+        <v>9.693936320000001</v>
       </c>
       <c r="O10">
-        <v>2.374420992</v>
+        <v>2.3265447168</v>
       </c>
       <c r="P10">
-        <v>7.518999808000001</v>
+        <v>7.367391603200001</v>
       </c>
       <c r="Q10">
-        <v>11.518999808</v>
+        <v>11.3673916032</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1112530061120466</v>
+        <v>0.1118103475584232</v>
       </c>
       <c r="T10">
-        <v>1.103631714252054</v>
+        <v>1.113029291726727</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.033674890116391</v>
+        <v>7.035835590279958</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1054615362781651</v>
+        <v>0.1052688669332473</v>
       </c>
       <c r="C11">
-        <v>307.8979231853145</v>
+        <v>305.6384717309401</v>
       </c>
       <c r="D11">
-        <v>316.9755231853145</v>
+        <v>318.0024717309401</v>
       </c>
       <c r="E11">
-        <v>26.83759999999999</v>
+        <v>30.124</v>
       </c>
       <c r="F11">
-        <v>29.5776</v>
+        <v>32.864</v>
       </c>
       <c r="G11">
         <v>20.5</v>
@@ -2171,28 +2171,28 @@
         <v>11.3</v>
       </c>
       <c r="M11">
-        <v>1.60606368</v>
+        <v>1.7845152</v>
       </c>
       <c r="N11">
-        <v>9.693936320000001</v>
+        <v>9.515484800000001</v>
       </c>
       <c r="O11">
-        <v>2.3265447168</v>
+        <v>2.283716352</v>
       </c>
       <c r="P11">
-        <v>7.367391603200001</v>
+        <v>7.231768448</v>
       </c>
       <c r="Q11">
-        <v>11.3673916032</v>
+        <v>11.231768448</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1118103475584232</v>
+        <v>0.1123800743702748</v>
       </c>
       <c r="T11">
-        <v>1.113029291726727</v>
+        <v>1.122635704256394</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.035835590279958</v>
+        <v>6.332252031251962</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1052688669332473</v>
+        <v>0.1051597975883295</v>
       </c>
       <c r="C12">
-        <v>305.6384717309401</v>
+        <v>302.9363783270387</v>
       </c>
       <c r="D12">
-        <v>318.0024717309401</v>
+        <v>318.5867783270386</v>
       </c>
       <c r="E12">
-        <v>30.124</v>
+        <v>33.4104</v>
       </c>
       <c r="F12">
-        <v>32.864</v>
+        <v>36.1504</v>
       </c>
       <c r="G12">
         <v>20.5</v>
@@ -2253,45 +2253,45 @@
         <v>11.3</v>
       </c>
       <c r="M12">
-        <v>1.7845152</v>
+        <v>1.99911712</v>
       </c>
       <c r="N12">
-        <v>9.515484800000001</v>
+        <v>9.300882880000001</v>
       </c>
       <c r="O12">
-        <v>2.283716352</v>
+        <v>2.2322118912</v>
       </c>
       <c r="P12">
-        <v>7.231768448</v>
+        <v>7.068670988800001</v>
       </c>
       <c r="Q12">
-        <v>11.231768448</v>
+        <v>11.0686709888</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1123800743702748</v>
+        <v>0.1129626040318309</v>
       </c>
       <c r="T12">
-        <v>1.122635704256394</v>
+        <v>1.13245799122493</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.332252031251962</v>
+        <v>5.652495237497642</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1051597975883295</v>
+        <v>0.1049747282434116</v>
       </c>
       <c r="C13">
-        <v>302.9363783270387</v>
+        <v>300.6463605346921</v>
       </c>
       <c r="D13">
-        <v>318.5867783270386</v>
+        <v>319.5831605346921</v>
       </c>
       <c r="E13">
-        <v>33.4104</v>
+        <v>36.6968</v>
       </c>
       <c r="F13">
-        <v>36.1504</v>
+        <v>39.4368</v>
       </c>
       <c r="G13">
         <v>20.5</v>
@@ -2335,28 +2335,28 @@
         <v>11.3</v>
       </c>
       <c r="M13">
-        <v>1.99911712</v>
+        <v>2.18085504</v>
       </c>
       <c r="N13">
-        <v>9.300882880000001</v>
+        <v>9.11914496</v>
       </c>
       <c r="O13">
-        <v>2.2322118912</v>
+        <v>2.1885947904</v>
       </c>
       <c r="P13">
-        <v>7.068670988800001</v>
+        <v>6.9305501696</v>
       </c>
       <c r="Q13">
-        <v>11.0686709888</v>
+        <v>10.9305501696</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1129626040318309</v>
+        <v>0.1135583730038769</v>
       </c>
       <c r="T13">
-        <v>1.13245799122493</v>
+        <v>1.142503511988204</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.652495237497642</v>
+        <v>5.181453967706171</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1049747282434116</v>
+        <v>0.1047896588984938</v>
       </c>
       <c r="C14">
-        <v>300.6463605346921</v>
+        <v>298.3625946789019</v>
       </c>
       <c r="D14">
-        <v>319.5831605346921</v>
+        <v>320.5857946789019</v>
       </c>
       <c r="E14">
-        <v>36.6968</v>
+        <v>39.9832</v>
       </c>
       <c r="F14">
-        <v>39.4368</v>
+        <v>42.7232</v>
       </c>
       <c r="G14">
         <v>20.5</v>
@@ -2417,28 +2417,28 @@
         <v>11.3</v>
       </c>
       <c r="M14">
-        <v>2.18085504</v>
+        <v>2.36259296</v>
       </c>
       <c r="N14">
-        <v>9.11914496</v>
+        <v>8.93740704</v>
       </c>
       <c r="O14">
-        <v>2.1885947904</v>
+        <v>2.1449776896</v>
       </c>
       <c r="P14">
-        <v>6.9305501696</v>
+        <v>6.7924293504</v>
       </c>
       <c r="Q14">
-        <v>10.9305501696</v>
+        <v>10.7924293504</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1135583730038769</v>
+        <v>0.1141678378143607</v>
       </c>
       <c r="T14">
-        <v>1.142503511988204</v>
+        <v>1.152779964263279</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.181453967706171</v>
+        <v>4.782880585574927</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1047896588984938</v>
+        <v>0.104870589553576</v>
       </c>
       <c r="C15">
-        <v>298.3625946789019</v>
+        <v>294.6369707170373</v>
       </c>
       <c r="D15">
-        <v>320.5857946789019</v>
+        <v>320.1465707170373</v>
       </c>
       <c r="E15">
-        <v>39.9832</v>
+        <v>43.2696</v>
       </c>
       <c r="F15">
-        <v>42.7232</v>
+        <v>46.0096</v>
       </c>
       <c r="G15">
         <v>20.5</v>
@@ -2499,45 +2499,45 @@
         <v>11.3</v>
       </c>
       <c r="M15">
-        <v>2.36259296</v>
+        <v>2.65935488</v>
       </c>
       <c r="N15">
-        <v>8.93740704</v>
+        <v>8.64064512</v>
       </c>
       <c r="O15">
-        <v>2.1449776896</v>
+        <v>2.0737548288</v>
       </c>
       <c r="P15">
-        <v>6.7924293504</v>
+        <v>6.5668902912</v>
       </c>
       <c r="Q15">
-        <v>10.7924293504</v>
+        <v>10.5668902912</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1141678378143607</v>
+        <v>0.1147914762250884</v>
       </c>
       <c r="T15">
-        <v>1.152779964263279</v>
+        <v>1.163295403800564</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.782880585574927</v>
+        <v>4.249150831648313</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.104870589553576</v>
+        <v>0.1051035202086582</v>
       </c>
       <c r="C16">
-        <v>294.6369707170373</v>
+        <v>290.0931082565114</v>
       </c>
       <c r="D16">
-        <v>320.1465707170373</v>
+        <v>318.8891082565113</v>
       </c>
       <c r="E16">
-        <v>43.2696</v>
+        <v>46.556</v>
       </c>
       <c r="F16">
-        <v>46.0096</v>
+        <v>49.29600000000001</v>
       </c>
       <c r="G16">
         <v>20.5</v>
@@ -2581,45 +2581,45 @@
         <v>11.3</v>
       </c>
       <c r="M16">
-        <v>2.65935488</v>
+        <v>3.0218448</v>
       </c>
       <c r="N16">
-        <v>8.64064512</v>
+        <v>8.2781552</v>
       </c>
       <c r="O16">
-        <v>2.0737548288</v>
+        <v>1.986757248</v>
       </c>
       <c r="P16">
-        <v>6.5668902912</v>
+        <v>6.291397952000001</v>
       </c>
       <c r="Q16">
-        <v>10.5668902912</v>
+        <v>10.291397952</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1147914762250884</v>
+        <v>0.1154297884807743</v>
       </c>
       <c r="T16">
-        <v>1.163295403800564</v>
+        <v>1.174058265444609</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.249150831648313</v>
+        <v>3.739437577998711</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1051035202086582</v>
+        <v>0.1049640508637404</v>
       </c>
       <c r="C17">
-        <v>290.0931082565114</v>
+        <v>287.5584359421695</v>
       </c>
       <c r="D17">
-        <v>318.8891082565113</v>
+        <v>319.6408359421695</v>
       </c>
       <c r="E17">
-        <v>46.556</v>
+        <v>49.8424</v>
       </c>
       <c r="F17">
-        <v>49.296</v>
+        <v>52.5824</v>
       </c>
       <c r="G17">
         <v>20.5</v>
@@ -2663,28 +2663,28 @@
         <v>11.3</v>
       </c>
       <c r="M17">
-        <v>3.0218448</v>
+        <v>3.22330112</v>
       </c>
       <c r="N17">
-        <v>8.2781552</v>
+        <v>8.07669888</v>
       </c>
       <c r="O17">
-        <v>1.986757248</v>
+        <v>1.9384077312</v>
       </c>
       <c r="P17">
-        <v>6.291397952000001</v>
+        <v>6.1382911488</v>
       </c>
       <c r="Q17">
-        <v>10.291397952</v>
+        <v>10.1382911488</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1154297884807743</v>
+        <v>0.11608329864731</v>
       </c>
       <c r="T17">
-        <v>1.174058265444609</v>
+        <v>1.185077385699226</v>
       </c>
       <c r="U17">
         <v>0.0613</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.739437577998712</v>
+        <v>3.505722729373792</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1049640508637404</v>
+        <v>0.1051863415188225</v>
       </c>
       <c r="C18">
-        <v>287.5584359421695</v>
+        <v>283.0755795012541</v>
       </c>
       <c r="D18">
-        <v>319.6408359421695</v>
+        <v>318.4443795012542</v>
       </c>
       <c r="E18">
-        <v>49.8424</v>
+        <v>53.1288</v>
       </c>
       <c r="F18">
-        <v>52.5824</v>
+        <v>55.8688</v>
       </c>
       <c r="G18">
         <v>20.5</v>
@@ -2745,45 +2745,45 @@
         <v>11.3</v>
       </c>
       <c r="M18">
-        <v>3.22330112</v>
+        <v>3.58119008</v>
       </c>
       <c r="N18">
-        <v>8.07669888</v>
+        <v>7.71880992</v>
       </c>
       <c r="O18">
-        <v>1.9384077312</v>
+        <v>1.8525143808</v>
       </c>
       <c r="P18">
-        <v>6.1382911488</v>
+        <v>5.8662955392</v>
       </c>
       <c r="Q18">
-        <v>10.1382911488</v>
+        <v>9.866295539199999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.11608329864731</v>
+        <v>0.1167525560467741</v>
       </c>
       <c r="T18">
-        <v>1.185077385699226</v>
+        <v>1.196362026923835</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.505722729373792</v>
+        <v>3.155375656575034</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1051863415188225</v>
+        <v>0.1061351921739047</v>
       </c>
       <c r="C19">
-        <v>283.0755795012541</v>
+        <v>274.7812206763929</v>
       </c>
       <c r="D19">
-        <v>318.4443795012542</v>
+        <v>313.4364206763929</v>
       </c>
       <c r="E19">
-        <v>53.1288</v>
+        <v>56.41520000000001</v>
       </c>
       <c r="F19">
-        <v>55.8688</v>
+        <v>59.15520000000001</v>
       </c>
       <c r="G19">
         <v>20.5</v>
@@ -2827,45 +2827,45 @@
         <v>11.3</v>
       </c>
       <c r="M19">
-        <v>3.58119008</v>
+        <v>4.253258880000001</v>
       </c>
       <c r="N19">
-        <v>7.71880992</v>
+        <v>7.04674112</v>
       </c>
       <c r="O19">
-        <v>1.8525143808</v>
+        <v>1.6912178688</v>
       </c>
       <c r="P19">
-        <v>5.8662955392</v>
+        <v>5.3555232512</v>
       </c>
       <c r="Q19">
-        <v>9.866295539199999</v>
+        <v>9.355523251200001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1167525560467741</v>
+        <v>0.1174381367974448</v>
       </c>
       <c r="T19">
-        <v>1.196362026923835</v>
+        <v>1.207921903300263</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.155375656575034</v>
+        <v>2.656786318165519</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1061351921739047</v>
+        <v>0.1060762828289869</v>
       </c>
       <c r="C20">
-        <v>274.7812206763929</v>
+        <v>271.8011490256014</v>
       </c>
       <c r="D20">
-        <v>313.4364206763929</v>
+        <v>313.7427490256014</v>
       </c>
       <c r="E20">
-        <v>56.41519999999999</v>
+        <v>59.7016</v>
       </c>
       <c r="F20">
-        <v>59.15519999999999</v>
+        <v>62.4416</v>
       </c>
       <c r="G20">
         <v>20.5</v>
@@ -2909,28 +2909,28 @@
         <v>11.3</v>
       </c>
       <c r="M20">
-        <v>4.25325888</v>
+        <v>4.48955104</v>
       </c>
       <c r="N20">
-        <v>7.046741120000001</v>
+        <v>6.81044896</v>
       </c>
       <c r="O20">
-        <v>1.6912178688</v>
+        <v>1.6345077504</v>
       </c>
       <c r="P20">
-        <v>5.355523251200001</v>
+        <v>5.1759412096</v>
       </c>
       <c r="Q20">
-        <v>9.355523251200001</v>
+        <v>9.175941209600001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1174381367974447</v>
+        <v>0.1181406454678851</v>
       </c>
       <c r="T20">
-        <v>1.207921903300262</v>
+        <v>1.219767208723022</v>
       </c>
       <c r="U20">
         <v>0.07190000000000001</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.65678631816552</v>
+        <v>2.516955459314703</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1060762828289869</v>
+        <v>0.1066101734840691</v>
       </c>
       <c r="C21">
-        <v>271.8011490256014</v>
+        <v>265.760204642523</v>
       </c>
       <c r="D21">
-        <v>313.7427490256014</v>
+        <v>310.988204642523</v>
       </c>
       <c r="E21">
-        <v>59.7016</v>
+        <v>62.98799999999999</v>
       </c>
       <c r="F21">
-        <v>62.4416</v>
+        <v>65.72799999999999</v>
       </c>
       <c r="G21">
         <v>20.5</v>
@@ -2991,45 +2991,45 @@
         <v>11.3</v>
       </c>
       <c r="M21">
-        <v>4.48955104</v>
+        <v>4.9821824</v>
       </c>
       <c r="N21">
-        <v>6.81044896</v>
+        <v>6.317817600000001</v>
       </c>
       <c r="O21">
-        <v>1.6345077504</v>
+        <v>1.516276224</v>
       </c>
       <c r="P21">
-        <v>5.1759412096</v>
+        <v>4.801541376</v>
       </c>
       <c r="Q21">
-        <v>9.175941209600001</v>
+        <v>8.801541375999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1181406454678851</v>
+        <v>0.1188607168550863</v>
       </c>
       <c r="T21">
-        <v>1.219767208723022</v>
+        <v>1.23190864678135</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.516955459314703</v>
+        <v>2.268082356840248</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1066101734840691</v>
+        <v>0.1065809041391513</v>
       </c>
       <c r="C22">
-        <v>265.760204642523</v>
+        <v>262.6235625501419</v>
       </c>
       <c r="D22">
-        <v>310.988204642523</v>
+        <v>311.1379625501419</v>
       </c>
       <c r="E22">
-        <v>62.98799999999999</v>
+        <v>66.27440000000001</v>
       </c>
       <c r="F22">
-        <v>65.72799999999999</v>
+        <v>69.01440000000001</v>
       </c>
       <c r="G22">
         <v>20.5</v>
@@ -3073,28 +3073,28 @@
         <v>11.3</v>
       </c>
       <c r="M22">
-        <v>4.9821824</v>
+        <v>5.231291520000001</v>
       </c>
       <c r="N22">
-        <v>6.317817600000001</v>
+        <v>6.06870848</v>
       </c>
       <c r="O22">
-        <v>1.516276224</v>
+        <v>1.4564900352</v>
       </c>
       <c r="P22">
-        <v>4.801541376</v>
+        <v>4.6122184448</v>
       </c>
       <c r="Q22">
-        <v>8.801541375999999</v>
+        <v>8.6122184448</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1188607168550863</v>
+        <v>0.1195990178976598</v>
       </c>
       <c r="T22">
-        <v>1.23190864678135</v>
+        <v>1.244357463018371</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.268082356840248</v>
+        <v>2.16007843508595</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1065809041391513</v>
+        <v>0.1065516347942334</v>
       </c>
       <c r="C23">
-        <v>262.6235625501419</v>
+        <v>259.487064760572</v>
       </c>
       <c r="D23">
-        <v>311.1379625501419</v>
+        <v>311.287864760572</v>
       </c>
       <c r="E23">
-        <v>66.2744</v>
+        <v>69.5608</v>
       </c>
       <c r="F23">
-        <v>69.01439999999999</v>
+        <v>72.3008</v>
       </c>
       <c r="G23">
         <v>20.5</v>
@@ -3155,28 +3155,28 @@
         <v>11.3</v>
       </c>
       <c r="M23">
-        <v>5.23129152</v>
+        <v>5.48040064</v>
       </c>
       <c r="N23">
-        <v>6.068708480000001</v>
+        <v>5.819599360000001</v>
       </c>
       <c r="O23">
-        <v>1.4564900352</v>
+        <v>1.3967038464</v>
       </c>
       <c r="P23">
-        <v>4.612218444800001</v>
+        <v>4.4228955136</v>
       </c>
       <c r="Q23">
-        <v>8.6122184448</v>
+        <v>8.4228955136</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1195990178976598</v>
+        <v>0.1203562497361967</v>
       </c>
       <c r="T23">
-        <v>1.244357463018371</v>
+        <v>1.257125479671725</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.16007843508595</v>
+        <v>2.061893051672953</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1065516347942334</v>
+        <v>0.1090045254493156</v>
       </c>
       <c r="C24">
-        <v>259.487064760572</v>
+        <v>244.1199618507148</v>
       </c>
       <c r="D24">
-        <v>311.287864760572</v>
+        <v>299.2071618507148</v>
       </c>
       <c r="E24">
-        <v>69.5608</v>
+        <v>72.8472</v>
       </c>
       <c r="F24">
-        <v>72.3008</v>
+        <v>75.5872</v>
       </c>
       <c r="G24">
         <v>20.5</v>
@@ -3237,45 +3237,45 @@
         <v>11.3</v>
       </c>
       <c r="M24">
-        <v>5.48040064</v>
+        <v>6.802847999999999</v>
       </c>
       <c r="N24">
-        <v>5.819599360000001</v>
+        <v>4.497152000000002</v>
       </c>
       <c r="O24">
-        <v>1.3967038464</v>
+        <v>1.07931648</v>
       </c>
       <c r="P24">
-        <v>4.4228955136</v>
+        <v>3.417835520000001</v>
       </c>
       <c r="Q24">
-        <v>8.4228955136</v>
+        <v>7.417835520000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1203562497361967</v>
+        <v>0.1211331499341761</v>
       </c>
       <c r="T24">
-        <v>1.257125479671725</v>
+        <v>1.27022513312127</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.061893051672953</v>
+        <v>1.661069011096529</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1090045254493156</v>
+        <v>0.1090831761043978</v>
       </c>
       <c r="C25">
-        <v>244.1199618507148</v>
+        <v>240.4616962027895</v>
       </c>
       <c r="D25">
-        <v>299.2071618507148</v>
+        <v>298.8352962027896</v>
       </c>
       <c r="E25">
-        <v>72.8472</v>
+        <v>76.1336</v>
       </c>
       <c r="F25">
-        <v>75.5872</v>
+        <v>78.8736</v>
       </c>
       <c r="G25">
         <v>20.5</v>
@@ -3319,28 +3319,28 @@
         <v>11.3</v>
       </c>
       <c r="M25">
-        <v>6.802847999999999</v>
+        <v>7.098623999999999</v>
       </c>
       <c r="N25">
-        <v>4.497152000000002</v>
+        <v>4.201376000000002</v>
       </c>
       <c r="O25">
-        <v>1.07931648</v>
+        <v>1.00833024</v>
       </c>
       <c r="P25">
-        <v>3.417835520000001</v>
+        <v>3.193045760000001</v>
       </c>
       <c r="Q25">
-        <v>7.417835520000001</v>
+        <v>7.193045760000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1211331499341761</v>
+        <v>0.1219304948742076</v>
       </c>
       <c r="T25">
-        <v>1.27022513312127</v>
+        <v>1.283669514293172</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.661069011096529</v>
+        <v>1.591857802300841</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1090831761043978</v>
+        <v>0.10916182675948</v>
       </c>
       <c r="C26">
-        <v>240.4616962027895</v>
+        <v>236.8043537440557</v>
       </c>
       <c r="D26">
-        <v>298.8352962027896</v>
+        <v>298.4643537440557</v>
       </c>
       <c r="E26">
-        <v>76.1336</v>
+        <v>79.42</v>
       </c>
       <c r="F26">
-        <v>78.8736</v>
+        <v>82.16</v>
       </c>
       <c r="G26">
         <v>20.5</v>
@@ -3401,28 +3401,28 @@
         <v>11.3</v>
       </c>
       <c r="M26">
-        <v>7.098623999999999</v>
+        <v>7.394399999999999</v>
       </c>
       <c r="N26">
-        <v>4.201376000000002</v>
+        <v>3.905600000000002</v>
       </c>
       <c r="O26">
-        <v>1.00833024</v>
+        <v>0.9373440000000003</v>
       </c>
       <c r="P26">
-        <v>3.193045760000001</v>
+        <v>2.968256000000001</v>
       </c>
       <c r="Q26">
-        <v>7.193045760000001</v>
+        <v>6.968256000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1219304948742076</v>
+        <v>0.1227491023459733</v>
       </c>
       <c r="T26">
-        <v>1.283669514293172</v>
+        <v>1.297472412296324</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.591857802300841</v>
+        <v>1.528183490208807</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.10916182675948</v>
+        <v>0.121752089688962</v>
       </c>
       <c r="C27">
-        <v>236.8043537440557</v>
+        <v>184.042755574996</v>
       </c>
       <c r="D27">
-        <v>298.4643537440557</v>
+        <v>248.9891555749959</v>
       </c>
       <c r="E27">
-        <v>79.42</v>
+        <v>82.7064</v>
       </c>
       <c r="F27">
-        <v>82.16</v>
+        <v>85.4464</v>
       </c>
       <c r="G27">
         <v>20.5</v>
@@ -3483,45 +3483,45 @@
         <v>11.3</v>
       </c>
       <c r="M27">
-        <v>7.394399999999999</v>
+        <v>12.54353152</v>
       </c>
       <c r="N27">
-        <v>3.905600000000002</v>
+        <v>-1.243531519999999</v>
       </c>
       <c r="O27">
-        <v>0.9373440000000003</v>
+        <v>-0.2984475647999998</v>
       </c>
       <c r="P27">
-        <v>2.968256000000001</v>
+        <v>-0.9450839551999997</v>
       </c>
       <c r="Q27">
-        <v>6.968256000000001</v>
+        <v>3.054916044800001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1227491023459733</v>
+        <v>0.1241030818055264</v>
       </c>
       <c r="T27">
-        <v>1.297472412296324</v>
+        <v>1.320302451140539</v>
       </c>
       <c r="U27">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.24</v>
+        <v>0.2162070542634551</v>
       </c>
       <c r="W27">
-        <v>0.0684</v>
+        <v>0.1150608044341248</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.528183490208807</v>
+        <v>0.9008627260977298</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.121752089688962</v>
+        <v>0.122762089688962</v>
       </c>
       <c r="C28">
-        <v>184.042755574996</v>
+        <v>177.4887851627699</v>
       </c>
       <c r="D28">
-        <v>248.9891555749959</v>
+        <v>245.7215851627699</v>
       </c>
       <c r="E28">
-        <v>82.7064</v>
+        <v>85.9928</v>
       </c>
       <c r="F28">
-        <v>85.4464</v>
+        <v>88.7328</v>
       </c>
       <c r="G28">
         <v>20.5</v>
@@ -3565,37 +3565,37 @@
         <v>11.3</v>
       </c>
       <c r="M28">
-        <v>12.54353152</v>
+        <v>13.02597504</v>
       </c>
       <c r="N28">
-        <v>-1.243531519999999</v>
+        <v>-1.72597504</v>
       </c>
       <c r="O28">
-        <v>-0.2984475647999998</v>
+        <v>-0.4142340096</v>
       </c>
       <c r="P28">
-        <v>-0.9450839551999997</v>
+        <v>-1.3117410304</v>
       </c>
       <c r="Q28">
-        <v>3.054916044800001</v>
+        <v>2.6882589696</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1241030818055264</v>
+        <v>0.1251757267617665</v>
       </c>
       <c r="T28">
-        <v>1.320302451140539</v>
+        <v>1.33838878608767</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.2162070542634551</v>
+        <v>0.2081993855870309</v>
       </c>
       <c r="W28">
-        <v>0.1150608044341248</v>
+        <v>0.1162363301958239</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.9008627260977298</v>
+        <v>0.8674974399459621</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.122762089688962</v>
+        <v>0.123772089688962</v>
       </c>
       <c r="C29">
-        <v>177.4887851627699</v>
+        <v>171.0194667363892</v>
       </c>
       <c r="D29">
-        <v>245.7215851627699</v>
+        <v>242.5386667363893</v>
       </c>
       <c r="E29">
-        <v>85.9928</v>
+        <v>89.2792</v>
       </c>
       <c r="F29">
-        <v>88.7328</v>
+        <v>92.0192</v>
       </c>
       <c r="G29">
         <v>20.5</v>
@@ -3647,37 +3647,37 @@
         <v>11.3</v>
       </c>
       <c r="M29">
-        <v>13.02597504</v>
+        <v>13.50841856</v>
       </c>
       <c r="N29">
-        <v>-1.72597504</v>
+        <v>-2.20841856</v>
       </c>
       <c r="O29">
-        <v>-0.4142340096</v>
+        <v>-0.5300204544</v>
       </c>
       <c r="P29">
-        <v>-1.3117410304</v>
+        <v>-1.6783981056</v>
       </c>
       <c r="Q29">
-        <v>2.6882589696</v>
+        <v>2.3216018944</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1251757267617665</v>
+        <v>0.1262781674112355</v>
       </c>
       <c r="T29">
-        <v>1.33838878608767</v>
+        <v>1.356977519227777</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.2081993855870309</v>
+        <v>0.2007636932446369</v>
       </c>
       <c r="W29">
-        <v>0.1162363301958239</v>
+        <v>0.1173278898316873</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8674974399459621</v>
+        <v>0.8365153885193205</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.123772089688962</v>
+        <v>0.124782089688962</v>
       </c>
       <c r="C30">
-        <v>171.0194667363892</v>
+        <v>164.6315527809033</v>
       </c>
       <c r="D30">
-        <v>242.5386667363893</v>
+        <v>239.4371527809033</v>
       </c>
       <c r="E30">
-        <v>89.2792</v>
+        <v>92.56560000000002</v>
       </c>
       <c r="F30">
-        <v>92.0192</v>
+        <v>95.30560000000001</v>
       </c>
       <c r="G30">
         <v>20.5</v>
@@ -3729,37 +3729,37 @@
         <v>11.3</v>
       </c>
       <c r="M30">
-        <v>13.50841856</v>
+        <v>13.99086208</v>
       </c>
       <c r="N30">
-        <v>-2.20841856</v>
+        <v>-2.690862080000002</v>
       </c>
       <c r="O30">
-        <v>-0.5300204544</v>
+        <v>-0.6458068992000006</v>
       </c>
       <c r="P30">
-        <v>-1.6783981056</v>
+        <v>-2.045055180800002</v>
       </c>
       <c r="Q30">
-        <v>2.3216018944</v>
+        <v>1.954944819199998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1262781674112355</v>
+        <v>0.1274116627268867</v>
       </c>
       <c r="T30">
-        <v>1.356977519227777</v>
+        <v>1.37608987865352</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.2007636932446369</v>
+        <v>0.1938408072706839</v>
       </c>
       <c r="W30">
-        <v>0.1173278898316873</v>
+        <v>0.1183441694926636</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8365153885193205</v>
+        <v>0.8076700302945162</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.124782089688962</v>
+        <v>0.1429202227153671</v>
       </c>
       <c r="C31">
-        <v>164.6315527809035</v>
+        <v>116.6279681701175</v>
       </c>
       <c r="D31">
-        <v>239.4371527809034</v>
+        <v>194.7199681701175</v>
       </c>
       <c r="E31">
-        <v>92.56559999999999</v>
+        <v>95.852</v>
       </c>
       <c r="F31">
-        <v>95.30559999999998</v>
+        <v>98.592</v>
       </c>
       <c r="G31">
         <v>20.5</v>
@@ -3811,45 +3811,45 @@
         <v>11.3</v>
       </c>
       <c r="M31">
-        <v>13.99086208</v>
+        <v>19.7972736</v>
       </c>
       <c r="N31">
-        <v>-2.690862079999999</v>
+        <v>-8.4972736</v>
       </c>
       <c r="O31">
-        <v>-0.6458068991999997</v>
+        <v>-2.039345664</v>
       </c>
       <c r="P31">
-        <v>-2.045055180799999</v>
+        <v>-6.457927936</v>
       </c>
       <c r="Q31">
-        <v>1.954944819200001</v>
+        <v>-2.457927936</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1274116627268867</v>
+        <v>0.1299034479464209</v>
       </c>
       <c r="T31">
-        <v>1.37608987865352</v>
+        <v>1.418104957207358</v>
       </c>
       <c r="U31">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.193840807270684</v>
+        <v>0.1369885598792755</v>
       </c>
       <c r="W31">
-        <v>0.1183441694926636</v>
+        <v>0.1732926971762415</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.8076700302945165</v>
+        <v>0.5707856661636479</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1429202227153671</v>
+        <v>0.1444702227153671</v>
       </c>
       <c r="C32">
-        <v>116.6279681701175</v>
+        <v>110.2827329677858</v>
       </c>
       <c r="D32">
-        <v>194.7199681701175</v>
+        <v>191.6611329677858</v>
       </c>
       <c r="E32">
-        <v>95.852</v>
+        <v>99.1384</v>
       </c>
       <c r="F32">
-        <v>98.592</v>
+        <v>101.8784</v>
       </c>
       <c r="G32">
         <v>20.5</v>
@@ -3893,37 +3893,37 @@
         <v>11.3</v>
       </c>
       <c r="M32">
-        <v>19.7972736</v>
+        <v>20.45718272</v>
       </c>
       <c r="N32">
-        <v>-8.4972736</v>
+        <v>-9.157182719999998</v>
       </c>
       <c r="O32">
-        <v>-2.039345664</v>
+        <v>-2.197723852799999</v>
       </c>
       <c r="P32">
-        <v>-6.457927936</v>
+        <v>-6.959458867199999</v>
       </c>
       <c r="Q32">
-        <v>-2.457927936</v>
+        <v>-2.959458867199999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1299034479464209</v>
+        <v>0.131122338496369</v>
       </c>
       <c r="T32">
-        <v>1.418104957207358</v>
+        <v>1.438657202963987</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1369885598792755</v>
+        <v>0.1325695740767182</v>
       </c>
       <c r="W32">
-        <v>0.1732926971762415</v>
+        <v>0.174180029525395</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5707856661636479</v>
+        <v>0.5523732253196594</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1444702227153671</v>
+        <v>0.146020222715367</v>
       </c>
       <c r="C33">
-        <v>110.2827329677858</v>
+        <v>104.0321132918449</v>
       </c>
       <c r="D33">
-        <v>191.6611329677858</v>
+        <v>188.6969132918449</v>
       </c>
       <c r="E33">
-        <v>99.1384</v>
+        <v>102.4248</v>
       </c>
       <c r="F33">
-        <v>101.8784</v>
+        <v>105.1648</v>
       </c>
       <c r="G33">
         <v>20.5</v>
@@ -3975,37 +3975,37 @@
         <v>11.3</v>
       </c>
       <c r="M33">
-        <v>20.45718272</v>
+        <v>21.11709184</v>
       </c>
       <c r="N33">
-        <v>-9.157182719999998</v>
+        <v>-9.81709184</v>
       </c>
       <c r="O33">
-        <v>-2.197723852799999</v>
+        <v>-2.3561020416</v>
       </c>
       <c r="P33">
-        <v>-6.959458867199999</v>
+        <v>-7.4609897984</v>
       </c>
       <c r="Q33">
-        <v>-2.959458867199999</v>
+        <v>-3.4609897984</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.131122338496369</v>
+        <v>0.1323770787683744</v>
       </c>
       <c r="T33">
-        <v>1.438657202963987</v>
+        <v>1.459813926536986</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1325695740767182</v>
+        <v>0.1284267748868208</v>
       </c>
       <c r="W33">
-        <v>0.174180029525395</v>
+        <v>0.1750119036027264</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5523732253196594</v>
+        <v>0.5351115620284199</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.146020222715367</v>
+        <v>0.147570222715367</v>
       </c>
       <c r="C34">
-        <v>104.0321132918449</v>
+        <v>97.87178604870255</v>
       </c>
       <c r="D34">
-        <v>188.6969132918449</v>
+        <v>185.8229860487025</v>
       </c>
       <c r="E34">
-        <v>102.4248</v>
+        <v>105.7112</v>
       </c>
       <c r="F34">
-        <v>105.1648</v>
+        <v>108.4512</v>
       </c>
       <c r="G34">
         <v>20.5</v>
@@ -4057,37 +4057,37 @@
         <v>11.3</v>
       </c>
       <c r="M34">
-        <v>21.11709184</v>
+        <v>21.77700096</v>
       </c>
       <c r="N34">
-        <v>-9.81709184</v>
+        <v>-10.47700096</v>
       </c>
       <c r="O34">
-        <v>-2.3561020416</v>
+        <v>-2.5144802304</v>
       </c>
       <c r="P34">
-        <v>-7.4609897984</v>
+        <v>-7.962520729600001</v>
       </c>
       <c r="Q34">
-        <v>-3.4609897984</v>
+        <v>-3.962520729600001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1323770787683744</v>
+        <v>0.1336692739738726</v>
       </c>
       <c r="T34">
-        <v>1.459813926536986</v>
+        <v>1.48160219409724</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1284267748868208</v>
+        <v>0.124535054435705</v>
       </c>
       <c r="W34">
-        <v>0.1750119036027264</v>
+        <v>0.1757933610693104</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5351115620284199</v>
+        <v>0.5188960601487709</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.147570222715367</v>
+        <v>0.1491202227153671</v>
       </c>
       <c r="C35">
-        <v>97.87178604870255</v>
+        <v>91.79768756329607</v>
       </c>
       <c r="D35">
-        <v>185.8229860487025</v>
+        <v>183.0352875632961</v>
       </c>
       <c r="E35">
-        <v>105.7112</v>
+        <v>108.9976</v>
       </c>
       <c r="F35">
-        <v>108.4512</v>
+        <v>111.7376</v>
       </c>
       <c r="G35">
         <v>20.5</v>
@@ -4139,37 +4139,37 @@
         <v>11.3</v>
       </c>
       <c r="M35">
-        <v>21.77700096</v>
+        <v>22.43691008</v>
       </c>
       <c r="N35">
-        <v>-10.47700096</v>
+        <v>-11.13691008</v>
       </c>
       <c r="O35">
-        <v>-2.5144802304</v>
+        <v>-2.6728584192</v>
       </c>
       <c r="P35">
-        <v>-7.962520729600001</v>
+        <v>-8.464051660799999</v>
       </c>
       <c r="Q35">
-        <v>-3.962520729600001</v>
+        <v>-4.464051660799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1336692739738726</v>
+        <v>0.1350006266098403</v>
       </c>
       <c r="T35">
-        <v>1.48160219409724</v>
+        <v>1.504050712189622</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.124535054435705</v>
+        <v>0.1208722587170078</v>
       </c>
       <c r="W35">
-        <v>0.1757933610693104</v>
+        <v>0.1765288504496249</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5188960601487709</v>
+        <v>0.5036344113208658</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1491202227153671</v>
+        <v>0.1632947356021253</v>
       </c>
       <c r="C36">
-        <v>91.79768756329607</v>
+        <v>66.42999150350471</v>
       </c>
       <c r="D36">
-        <v>183.0352875632961</v>
+        <v>160.9539915035047</v>
       </c>
       <c r="E36">
-        <v>108.9976</v>
+        <v>112.284</v>
       </c>
       <c r="F36">
-        <v>111.7376</v>
+        <v>115.024</v>
       </c>
       <c r="G36">
         <v>20.5</v>
@@ -4221,45 +4221,45 @@
         <v>11.3</v>
       </c>
       <c r="M36">
-        <v>22.43691008</v>
+        <v>27.1226592</v>
       </c>
       <c r="N36">
-        <v>-11.13691008</v>
+        <v>-15.8226592</v>
       </c>
       <c r="O36">
-        <v>-2.6728584192</v>
+        <v>-3.797438208</v>
       </c>
       <c r="P36">
-        <v>-8.464051660799999</v>
+        <v>-12.025220992</v>
       </c>
       <c r="Q36">
-        <v>-4.464051660799999</v>
+        <v>-8.025220992000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1350006266098403</v>
+        <v>0.1369491176142351</v>
       </c>
       <c r="T36">
-        <v>1.504050712189622</v>
+        <v>1.536905069767999</v>
       </c>
       <c r="U36">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1208722587170078</v>
+        <v>0.09999019565161221</v>
       </c>
       <c r="W36">
-        <v>0.1765288504496249</v>
+        <v>0.2122223118653498</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.5036344113208658</v>
+        <v>0.4166258152150509</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1632947356021253</v>
+        <v>0.1651947356021252</v>
       </c>
       <c r="C37">
-        <v>66.42999150350471</v>
+        <v>60.58223415123618</v>
       </c>
       <c r="D37">
-        <v>160.9539915035047</v>
+        <v>158.3926341512362</v>
       </c>
       <c r="E37">
-        <v>112.284</v>
+        <v>115.5704</v>
       </c>
       <c r="F37">
-        <v>115.024</v>
+        <v>118.3104</v>
       </c>
       <c r="G37">
         <v>20.5</v>
@@ -4303,37 +4303,37 @@
         <v>11.3</v>
       </c>
       <c r="M37">
-        <v>27.1226592</v>
+        <v>27.89759232</v>
       </c>
       <c r="N37">
-        <v>-15.8226592</v>
+        <v>-16.59759232</v>
       </c>
       <c r="O37">
-        <v>-3.797438208</v>
+        <v>-3.983422156800001</v>
       </c>
       <c r="P37">
-        <v>-12.025220992</v>
+        <v>-12.6141701632</v>
       </c>
       <c r="Q37">
-        <v>-8.025220992000001</v>
+        <v>-8.614170163200003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1369491176142351</v>
+        <v>0.1383733225769575</v>
       </c>
       <c r="T37">
-        <v>1.536905069767999</v>
+        <v>1.560919211483125</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.09999019565161221</v>
+        <v>0.0972126902168452</v>
       </c>
       <c r="W37">
-        <v>0.2122223118653498</v>
+        <v>0.2128772476468679</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4166258152150509</v>
+        <v>0.4050528759035217</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1651947356021252</v>
+        <v>0.1670947356021253</v>
       </c>
       <c r="C38">
-        <v>60.58223415123621</v>
+        <v>54.81472066025567</v>
       </c>
       <c r="D38">
-        <v>158.3926341512362</v>
+        <v>155.9115206602557</v>
       </c>
       <c r="E38">
-        <v>115.5704</v>
+        <v>118.8568</v>
       </c>
       <c r="F38">
-        <v>118.3104</v>
+        <v>121.5968</v>
       </c>
       <c r="G38">
         <v>20.5</v>
@@ -4385,37 +4385,37 @@
         <v>11.3</v>
       </c>
       <c r="M38">
-        <v>27.89759232</v>
+        <v>28.67252544</v>
       </c>
       <c r="N38">
-        <v>-16.59759232</v>
+        <v>-17.37252544</v>
       </c>
       <c r="O38">
-        <v>-3.983422156799999</v>
+        <v>-4.169406105599999</v>
       </c>
       <c r="P38">
-        <v>-12.6141701632</v>
+        <v>-13.2031193344</v>
       </c>
       <c r="Q38">
-        <v>-8.614170163199997</v>
+        <v>-9.203119334399997</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1383733225769575</v>
+        <v>0.1398427403956394</v>
       </c>
       <c r="T38">
-        <v>1.560919211483125</v>
+        <v>1.585695706903491</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.09721269021684521</v>
+        <v>0.09458532021098454</v>
       </c>
       <c r="W38">
-        <v>0.2128772476468679</v>
+        <v>0.2134967814942499</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4050528759035218</v>
+        <v>0.3941055008791022</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1670947356021253</v>
+        <v>0.1689947356021252</v>
       </c>
       <c r="C39">
-        <v>54.81472066025567</v>
+        <v>49.12373829067128</v>
       </c>
       <c r="D39">
-        <v>155.9115206602557</v>
+        <v>153.5069382906713</v>
       </c>
       <c r="E39">
-        <v>118.8568</v>
+        <v>122.1432</v>
       </c>
       <c r="F39">
-        <v>121.5968</v>
+        <v>124.8832</v>
       </c>
       <c r="G39">
         <v>20.5</v>
@@ -4467,37 +4467,37 @@
         <v>11.3</v>
       </c>
       <c r="M39">
-        <v>28.67252544</v>
+        <v>29.44745856</v>
       </c>
       <c r="N39">
-        <v>-17.37252544</v>
+        <v>-18.14745856</v>
       </c>
       <c r="O39">
-        <v>-4.169406105599999</v>
+        <v>-4.3553900544</v>
       </c>
       <c r="P39">
-        <v>-13.2031193344</v>
+        <v>-13.7920685056</v>
       </c>
       <c r="Q39">
-        <v>-9.203119334399997</v>
+        <v>-9.7920685056</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1398427403956394</v>
+        <v>0.1413595587891174</v>
       </c>
       <c r="T39">
-        <v>1.585695706903491</v>
+        <v>1.611271444111612</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09458532021098454</v>
+        <v>0.09209623283701125</v>
       </c>
       <c r="W39">
-        <v>0.2134967814942499</v>
+        <v>0.2140837082970327</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3941055008791022</v>
+        <v>0.3837343034875469</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1689947356021252</v>
+        <v>0.1708947356021253</v>
       </c>
       <c r="C40">
-        <v>49.12373829067128</v>
+        <v>43.50579986622517</v>
       </c>
       <c r="D40">
-        <v>153.5069382906713</v>
+        <v>151.1753998662252</v>
       </c>
       <c r="E40">
-        <v>122.1432</v>
+        <v>125.4296</v>
       </c>
       <c r="F40">
-        <v>124.8832</v>
+        <v>128.1696</v>
       </c>
       <c r="G40">
         <v>20.5</v>
@@ -4549,37 +4549,37 @@
         <v>11.3</v>
       </c>
       <c r="M40">
-        <v>29.44745856</v>
+        <v>30.22239168</v>
       </c>
       <c r="N40">
-        <v>-18.14745856</v>
+        <v>-18.92239168</v>
       </c>
       <c r="O40">
-        <v>-4.3553900544</v>
+        <v>-4.5413740032</v>
       </c>
       <c r="P40">
-        <v>-13.7920685056</v>
+        <v>-14.3810176768</v>
       </c>
       <c r="Q40">
-        <v>-9.7920685056</v>
+        <v>-10.3810176768</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1413595587891174</v>
+        <v>0.1429261089332013</v>
       </c>
       <c r="T40">
-        <v>1.611271444111612</v>
+        <v>1.637685730080655</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.09209623283701125</v>
+        <v>0.08973479096939559</v>
       </c>
       <c r="W40">
-        <v>0.2140837082970327</v>
+        <v>0.2146405362894165</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3837343034875469</v>
+        <v>0.3738949623724815</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1708947356021253</v>
+        <v>0.1727947356021253</v>
       </c>
       <c r="C41">
-        <v>43.50579986622517</v>
+        <v>37.95762690072422</v>
       </c>
       <c r="D41">
-        <v>151.1753998662252</v>
+        <v>148.9136269007242</v>
       </c>
       <c r="E41">
-        <v>125.4296</v>
+        <v>128.716</v>
       </c>
       <c r="F41">
-        <v>128.1696</v>
+        <v>131.456</v>
       </c>
       <c r="G41">
         <v>20.5</v>
@@ -4631,37 +4631,37 @@
         <v>11.3</v>
       </c>
       <c r="M41">
-        <v>30.22239168</v>
+        <v>30.9973248</v>
       </c>
       <c r="N41">
-        <v>-18.92239168</v>
+        <v>-19.6973248</v>
       </c>
       <c r="O41">
-        <v>-4.5413740032</v>
+        <v>-4.727357951999999</v>
       </c>
       <c r="P41">
-        <v>-14.3810176768</v>
+        <v>-14.969966848</v>
       </c>
       <c r="Q41">
-        <v>-10.3810176768</v>
+        <v>-10.969966848</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1429261089332013</v>
+        <v>0.1445448774154214</v>
       </c>
       <c r="T41">
-        <v>1.637685730080655</v>
+        <v>1.664980492248666</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08973479096939559</v>
+        <v>0.08749142119516069</v>
       </c>
       <c r="W41">
-        <v>0.2146405362894165</v>
+        <v>0.2151695228821811</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3738949623724815</v>
+        <v>0.3645475883131696</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1727947356021253</v>
+        <v>0.1746947356021252</v>
       </c>
       <c r="C42">
-        <v>37.95762690072422</v>
+        <v>32.47613421684034</v>
       </c>
       <c r="D42">
-        <v>148.9136269007242</v>
+        <v>146.7185342168403</v>
       </c>
       <c r="E42">
-        <v>128.716</v>
+        <v>132.0024</v>
       </c>
       <c r="F42">
-        <v>131.456</v>
+        <v>134.7424</v>
       </c>
       <c r="G42">
         <v>20.5</v>
@@ -4713,37 +4713,37 @@
         <v>11.3</v>
       </c>
       <c r="M42">
-        <v>30.9973248</v>
+        <v>31.77225792</v>
       </c>
       <c r="N42">
-        <v>-19.6973248</v>
+        <v>-20.47225792</v>
       </c>
       <c r="O42">
-        <v>-4.727357951999999</v>
+        <v>-4.9133419008</v>
       </c>
       <c r="P42">
-        <v>-14.969966848</v>
+        <v>-15.5589160192</v>
       </c>
       <c r="Q42">
-        <v>-10.969966848</v>
+        <v>-11.5589160192</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1445448774154214</v>
+        <v>0.1462185194055132</v>
       </c>
       <c r="T42">
-        <v>1.664980492248666</v>
+        <v>1.693200500591864</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08749142119516069</v>
+        <v>0.08535748409283969</v>
       </c>
       <c r="W42">
-        <v>0.2151695228821811</v>
+        <v>0.2156727052509084</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3645475883131696</v>
+        <v>0.3556561837201654</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1746947356021252</v>
+        <v>0.1765947356021253</v>
       </c>
       <c r="C43">
-        <v>32.47613421684034</v>
+        <v>27.05841590552848</v>
       </c>
       <c r="D43">
-        <v>146.7185342168403</v>
+        <v>144.5872159055285</v>
       </c>
       <c r="E43">
-        <v>132.0024</v>
+        <v>135.2888</v>
       </c>
       <c r="F43">
-        <v>134.7424</v>
+        <v>138.0288</v>
       </c>
       <c r="G43">
         <v>20.5</v>
@@ -4795,37 +4795,37 @@
         <v>11.3</v>
       </c>
       <c r="M43">
-        <v>31.77225792</v>
+        <v>32.54719104000001</v>
       </c>
       <c r="N43">
-        <v>-20.47225792</v>
+        <v>-21.24719104000001</v>
       </c>
       <c r="O43">
-        <v>-4.9133419008</v>
+        <v>-5.099325849600001</v>
       </c>
       <c r="P43">
-        <v>-15.5589160192</v>
+        <v>-16.1478651904</v>
       </c>
       <c r="Q43">
-        <v>-11.5589160192</v>
+        <v>-12.1478651904</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1462185194055132</v>
+        <v>0.1479498731883669</v>
       </c>
       <c r="T43">
-        <v>1.693200500591864</v>
+        <v>1.722393612671034</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08535748409283969</v>
+        <v>0.08332516304301016</v>
       </c>
       <c r="W43">
-        <v>0.2156727052509084</v>
+        <v>0.2161519265544582</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3556561837201654</v>
+        <v>0.3471881793458756</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1765947356021252</v>
+        <v>0.1784947356021253</v>
       </c>
       <c r="C44">
-        <v>27.05841590552853</v>
+        <v>21.70173249169198</v>
       </c>
       <c r="D44">
-        <v>144.5872159055285</v>
+        <v>142.516932491692</v>
       </c>
       <c r="E44">
-        <v>135.2888</v>
+        <v>138.5752</v>
       </c>
       <c r="F44">
-        <v>138.0288</v>
+        <v>141.3152</v>
       </c>
       <c r="G44">
         <v>20.5</v>
@@ -4877,37 +4877,37 @@
         <v>11.3</v>
       </c>
       <c r="M44">
-        <v>32.54719104</v>
+        <v>33.32212416</v>
       </c>
       <c r="N44">
-        <v>-21.24719104</v>
+        <v>-22.02212416</v>
       </c>
       <c r="O44">
-        <v>-5.0993258496</v>
+        <v>-5.2853097984</v>
       </c>
       <c r="P44">
-        <v>-16.1478651904</v>
+        <v>-16.7368143616</v>
       </c>
       <c r="Q44">
-        <v>-12.1478651904</v>
+        <v>-12.7368143616</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1479498731883669</v>
+        <v>0.1497419762267593</v>
       </c>
       <c r="T44">
-        <v>1.722393612671034</v>
+        <v>1.75261104447228</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08332516304301017</v>
+        <v>0.08138736855363785</v>
       </c>
       <c r="W44">
-        <v>0.2161519265544582</v>
+        <v>0.2166088584950522</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3471881793458758</v>
+        <v>0.3391140356401577</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1784947356021253</v>
+        <v>0.1803947356021253</v>
       </c>
       <c r="C45">
-        <v>21.70173249169198</v>
+        <v>16.40349918689861</v>
       </c>
       <c r="D45">
-        <v>142.516932491692</v>
+        <v>140.5050991868986</v>
       </c>
       <c r="E45">
-        <v>138.5752</v>
+        <v>141.8616</v>
       </c>
       <c r="F45">
-        <v>141.3152</v>
+        <v>144.6016</v>
       </c>
       <c r="G45">
         <v>20.5</v>
@@ -4959,37 +4959,37 @@
         <v>11.3</v>
       </c>
       <c r="M45">
-        <v>33.32212416</v>
+        <v>34.09705728</v>
       </c>
       <c r="N45">
-        <v>-22.02212416</v>
+        <v>-22.79705728</v>
       </c>
       <c r="O45">
-        <v>-5.2853097984</v>
+        <v>-5.4712937472</v>
       </c>
       <c r="P45">
-        <v>-16.7368143616</v>
+        <v>-17.3257635328</v>
       </c>
       <c r="Q45">
-        <v>-12.7368143616</v>
+        <v>-13.3257635328</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1497419762267593</v>
+        <v>0.1515980829450943</v>
       </c>
       <c r="T45">
-        <v>1.75261104447228</v>
+        <v>1.783907670266428</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08138736855363785</v>
+        <v>0.07953765563196426</v>
       </c>
       <c r="W45">
-        <v>0.2166088584950522</v>
+        <v>0.2170450208019828</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3391140356401577</v>
+        <v>0.3314068984665177</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1803947356021253</v>
+        <v>0.1822947356021253</v>
       </c>
       <c r="C46">
-        <v>16.40349918689861</v>
+        <v>11.16127512322714</v>
       </c>
       <c r="D46">
-        <v>140.5050991868986</v>
+        <v>138.5492751232271</v>
       </c>
       <c r="E46">
-        <v>141.8616</v>
+        <v>145.148</v>
       </c>
       <c r="F46">
-        <v>144.6016</v>
+        <v>147.888</v>
       </c>
       <c r="G46">
         <v>20.5</v>
@@ -5041,37 +5041,37 @@
         <v>11.3</v>
       </c>
       <c r="M46">
-        <v>34.09705728</v>
+        <v>34.8719904</v>
       </c>
       <c r="N46">
-        <v>-22.79705728</v>
+        <v>-23.5719904</v>
       </c>
       <c r="O46">
-        <v>-5.4712937472</v>
+        <v>-5.657277696</v>
       </c>
       <c r="P46">
-        <v>-17.3257635328</v>
+        <v>-17.914712704</v>
       </c>
       <c r="Q46">
-        <v>-13.3257635328</v>
+        <v>-13.914712704</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1515980829450943</v>
+        <v>0.1535216844531869</v>
       </c>
       <c r="T46">
-        <v>1.783907670266428</v>
+        <v>1.816342355180363</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07953765563196426</v>
+        <v>0.07777015217347616</v>
       </c>
       <c r="W46">
-        <v>0.2170450208019828</v>
+        <v>0.2174617981174943</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3314068984665177</v>
+        <v>0.3240423007228174</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1822947356021253</v>
+        <v>0.1841947356021253</v>
       </c>
       <c r="C47">
-        <v>11.16127512322714</v>
+        <v>5.972753473954782</v>
       </c>
       <c r="D47">
-        <v>138.5492751232271</v>
+        <v>136.6471534739548</v>
       </c>
       <c r="E47">
-        <v>145.148</v>
+        <v>148.4344</v>
       </c>
       <c r="F47">
-        <v>147.888</v>
+        <v>151.1744</v>
       </c>
       <c r="G47">
         <v>20.5</v>
@@ -5123,37 +5123,37 @@
         <v>11.3</v>
       </c>
       <c r="M47">
-        <v>34.8719904</v>
+        <v>35.64692352</v>
       </c>
       <c r="N47">
-        <v>-23.5719904</v>
+        <v>-24.34692352</v>
       </c>
       <c r="O47">
-        <v>-5.657277696</v>
+        <v>-5.8432616448</v>
       </c>
       <c r="P47">
-        <v>-17.914712704</v>
+        <v>-18.5036618752</v>
       </c>
       <c r="Q47">
-        <v>-13.914712704</v>
+        <v>-14.5036618752</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1535216844531869</v>
+        <v>0.1555165304615793</v>
       </c>
       <c r="T47">
-        <v>1.816342355180363</v>
+        <v>1.84997832472074</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07777015217347616</v>
+        <v>0.07607949669144408</v>
       </c>
       <c r="W47">
-        <v>0.2174617981174943</v>
+        <v>0.2178604546801575</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3240423007228174</v>
+        <v>0.316997902881017</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1841947356021253</v>
+        <v>0.1860947356021253</v>
       </c>
       <c r="C48">
-        <v>5.972753473954782</v>
+        <v>0.8357523770124828</v>
       </c>
       <c r="D48">
-        <v>136.6471534739548</v>
+        <v>134.7965523770125</v>
       </c>
       <c r="E48">
-        <v>148.4344</v>
+        <v>151.7208</v>
       </c>
       <c r="F48">
-        <v>151.1744</v>
+        <v>154.4608</v>
       </c>
       <c r="G48">
         <v>20.5</v>
@@ -5205,37 +5205,37 @@
         <v>11.3</v>
       </c>
       <c r="M48">
-        <v>35.64692352</v>
+        <v>36.42185664</v>
       </c>
       <c r="N48">
-        <v>-24.34692352</v>
+        <v>-25.12185664</v>
       </c>
       <c r="O48">
-        <v>-5.8432616448</v>
+        <v>-6.0292455936</v>
       </c>
       <c r="P48">
-        <v>-18.5036618752</v>
+        <v>-19.0926110464</v>
       </c>
       <c r="Q48">
-        <v>-14.5036618752</v>
+        <v>-15.0926110464</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1555165304615793</v>
+        <v>0.1575866536778355</v>
       </c>
       <c r="T48">
-        <v>1.84997832472074</v>
+        <v>1.884883576130565</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07607949669144408</v>
+        <v>0.07446078399588144</v>
       </c>
       <c r="W48">
-        <v>0.2178604546801575</v>
+        <v>0.2182421471337712</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.316997902881017</v>
+        <v>0.310253266649506</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1860947356021253</v>
+        <v>0.1879947356021253</v>
       </c>
       <c r="C49">
-        <v>0.8357523770124828</v>
+        <v>-4.251793413876328</v>
       </c>
       <c r="D49">
-        <v>134.7965523770125</v>
+        <v>132.9954065861237</v>
       </c>
       <c r="E49">
-        <v>151.7208</v>
+        <v>155.0072</v>
       </c>
       <c r="F49">
-        <v>154.4608</v>
+        <v>157.7472</v>
       </c>
       <c r="G49">
         <v>20.5</v>
@@ -5287,37 +5287,37 @@
         <v>11.3</v>
       </c>
       <c r="M49">
-        <v>36.42185664</v>
+        <v>37.19678976</v>
       </c>
       <c r="N49">
-        <v>-25.12185664</v>
+        <v>-25.89678976</v>
       </c>
       <c r="O49">
-        <v>-6.0292455936</v>
+        <v>-6.2152295424</v>
       </c>
       <c r="P49">
-        <v>-19.0926110464</v>
+        <v>-19.6815602176</v>
       </c>
       <c r="Q49">
-        <v>-15.0926110464</v>
+        <v>-15.6815602176</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1575866536778355</v>
+        <v>0.1597363970177939</v>
       </c>
       <c r="T49">
-        <v>1.884883576130565</v>
+        <v>1.921131337209999</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07446078399588144</v>
+        <v>0.0729095176626339</v>
       </c>
       <c r="W49">
-        <v>0.2182421471337712</v>
+        <v>0.2186079357351509</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.310253266649506</v>
+        <v>0.3037896569276413</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1879947356021253</v>
+        <v>0.1898947356021252</v>
       </c>
       <c r="C50">
-        <v>-4.251793413876328</v>
+        <v>-9.291840217541392</v>
       </c>
       <c r="D50">
-        <v>132.9954065861237</v>
+        <v>131.2417597824586</v>
       </c>
       <c r="E50">
-        <v>155.0072</v>
+        <v>158.2936</v>
       </c>
       <c r="F50">
-        <v>157.7472</v>
+        <v>161.0336</v>
       </c>
       <c r="G50">
         <v>20.5</v>
@@ -5369,37 +5369,37 @@
         <v>11.3</v>
       </c>
       <c r="M50">
-        <v>37.19678976</v>
+        <v>37.97172287999999</v>
       </c>
       <c r="N50">
-        <v>-25.89678976</v>
+        <v>-26.67172287999999</v>
       </c>
       <c r="O50">
-        <v>-6.2152295424</v>
+        <v>-6.401213491199998</v>
       </c>
       <c r="P50">
-        <v>-19.6815602176</v>
+        <v>-20.27050938879999</v>
       </c>
       <c r="Q50">
-        <v>-15.6815602176</v>
+        <v>-16.27050938879999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1597363970177939</v>
+        <v>0.1619704440181428</v>
       </c>
       <c r="T50">
-        <v>1.921131337209999</v>
+        <v>1.958800579116078</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0729095176626339</v>
+        <v>0.07142156832258016</v>
       </c>
       <c r="W50">
-        <v>0.2186079357351509</v>
+        <v>0.2189587941895356</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3037896569276413</v>
+        <v>0.2975898680107507</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1898947356021252</v>
+        <v>0.1917947356021253</v>
       </c>
       <c r="C51">
-        <v>-9.291840217541392</v>
+        <v>-14.28624251336558</v>
       </c>
       <c r="D51">
-        <v>131.2417597824586</v>
+        <v>129.5337574866344</v>
       </c>
       <c r="E51">
-        <v>158.2936</v>
+        <v>161.58</v>
       </c>
       <c r="F51">
-        <v>161.0336</v>
+        <v>164.32</v>
       </c>
       <c r="G51">
         <v>20.5</v>
@@ -5451,37 +5451,37 @@
         <v>11.3</v>
       </c>
       <c r="M51">
-        <v>37.97172287999999</v>
+        <v>38.746656</v>
       </c>
       <c r="N51">
-        <v>-26.67172287999999</v>
+        <v>-27.446656</v>
       </c>
       <c r="O51">
-        <v>-6.401213491199998</v>
+        <v>-6.58719744</v>
       </c>
       <c r="P51">
-        <v>-20.27050938879999</v>
+        <v>-20.85945856</v>
       </c>
       <c r="Q51">
-        <v>-16.27050938879999</v>
+        <v>-16.85945856</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1619704440181428</v>
+        <v>0.1642938528985056</v>
       </c>
       <c r="T51">
-        <v>1.958800579116078</v>
+        <v>1.997976590698399</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07142156832258016</v>
+        <v>0.06999313695612855</v>
       </c>
       <c r="W51">
-        <v>0.2189587941895356</v>
+        <v>0.2192956183057449</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2975898680107507</v>
+        <v>0.2916380706505356</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1917947356021253</v>
+        <v>0.1936947356021252</v>
       </c>
       <c r="C52">
-        <v>-14.28624251336558</v>
+        <v>-19.23675948292913</v>
       </c>
       <c r="D52">
-        <v>129.5337574866344</v>
+        <v>127.8696405170709</v>
       </c>
       <c r="E52">
-        <v>161.58</v>
+        <v>164.8664</v>
       </c>
       <c r="F52">
-        <v>164.32</v>
+        <v>167.6064</v>
       </c>
       <c r="G52">
         <v>20.5</v>
@@ -5533,37 +5533,37 @@
         <v>11.3</v>
       </c>
       <c r="M52">
-        <v>38.746656</v>
+        <v>39.52158912</v>
       </c>
       <c r="N52">
-        <v>-27.446656</v>
+        <v>-28.22158912</v>
       </c>
       <c r="O52">
-        <v>-6.58719744</v>
+        <v>-6.7731813888</v>
       </c>
       <c r="P52">
-        <v>-20.85945856</v>
+        <v>-21.4484077312</v>
       </c>
       <c r="Q52">
-        <v>-16.85945856</v>
+        <v>-17.4484077312</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1642938528985056</v>
+        <v>0.1667120947943935</v>
       </c>
       <c r="T52">
-        <v>1.997976590698399</v>
+        <v>2.038751623161632</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06999313695612855</v>
+        <v>0.06862072250600837</v>
       </c>
       <c r="W52">
-        <v>0.2192956183057449</v>
+        <v>0.2196192336330832</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2916380706505356</v>
+        <v>0.2859196771083683</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1936947356021252</v>
+        <v>0.1955947356021253</v>
       </c>
       <c r="C53">
-        <v>-19.23675948292913</v>
+        <v>-24.14506105380775</v>
       </c>
       <c r="D53">
-        <v>127.8696405170709</v>
+        <v>126.2477389461922</v>
       </c>
       <c r="E53">
-        <v>164.8664</v>
+        <v>168.1528</v>
       </c>
       <c r="F53">
-        <v>167.6064</v>
+        <v>170.8928</v>
       </c>
       <c r="G53">
         <v>20.5</v>
@@ -5615,37 +5615,37 @@
         <v>11.3</v>
       </c>
       <c r="M53">
-        <v>39.52158912</v>
+        <v>40.29652224</v>
       </c>
       <c r="N53">
-        <v>-28.22158912</v>
+        <v>-28.99652224</v>
       </c>
       <c r="O53">
-        <v>-6.7731813888</v>
+        <v>-6.9591653376</v>
       </c>
       <c r="P53">
-        <v>-21.4484077312</v>
+        <v>-22.0373569024</v>
       </c>
       <c r="Q53">
-        <v>-17.4484077312</v>
+        <v>-18.0373569024</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1667120947943935</v>
+        <v>0.1692310967692767</v>
       </c>
       <c r="T53">
-        <v>2.038751623161632</v>
+        <v>2.081225615310832</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06862072250600837</v>
+        <v>0.06730109322704668</v>
       </c>
       <c r="W53">
-        <v>0.2196192336330832</v>
+        <v>0.2199304022170624</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2859196771083683</v>
+        <v>0.2804212217793611</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1955947356021253</v>
+        <v>0.1974947356021253</v>
       </c>
       <c r="C54">
-        <v>-24.14506105380775</v>
+        <v>-29.01273348917368</v>
       </c>
       <c r="D54">
-        <v>126.2477389461922</v>
+        <v>124.6664665108263</v>
       </c>
       <c r="E54">
-        <v>168.1528</v>
+        <v>171.4392</v>
       </c>
       <c r="F54">
-        <v>170.8928</v>
+        <v>174.1792</v>
       </c>
       <c r="G54">
         <v>20.5</v>
@@ -5697,37 +5697,37 @@
         <v>11.3</v>
       </c>
       <c r="M54">
-        <v>40.29652224</v>
+        <v>41.07145536</v>
       </c>
       <c r="N54">
-        <v>-28.99652224</v>
+        <v>-29.77145536</v>
       </c>
       <c r="O54">
-        <v>-6.9591653376</v>
+        <v>-7.1451492864</v>
       </c>
       <c r="P54">
-        <v>-22.0373569024</v>
+        <v>-22.6263060736</v>
       </c>
       <c r="Q54">
-        <v>-18.0373569024</v>
+        <v>-18.6263060736</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1692310967692767</v>
+        <v>0.1718572903175592</v>
       </c>
       <c r="T54">
-        <v>2.081225615310832</v>
+        <v>2.125507011381276</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06730109322704668</v>
+        <v>0.06603126127936657</v>
       </c>
       <c r="W54">
-        <v>0.2199304022170624</v>
+        <v>0.2202298285903254</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2804212217793611</v>
+        <v>0.275130255330694</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1974947356021253</v>
+        <v>0.1993947356021253</v>
       </c>
       <c r="C55">
-        <v>-29.01273348917368</v>
+        <v>-33.84128456252918</v>
       </c>
       <c r="D55">
-        <v>124.6664665108263</v>
+        <v>123.1243154374708</v>
       </c>
       <c r="E55">
-        <v>171.4392</v>
+        <v>174.7256</v>
       </c>
       <c r="F55">
-        <v>174.1792</v>
+        <v>177.4656</v>
       </c>
       <c r="G55">
         <v>20.5</v>
@@ -5779,37 +5779,37 @@
         <v>11.3</v>
       </c>
       <c r="M55">
-        <v>41.07145536</v>
+        <v>41.84638848</v>
       </c>
       <c r="N55">
-        <v>-29.77145536</v>
+        <v>-30.54638848</v>
       </c>
       <c r="O55">
-        <v>-7.1451492864</v>
+        <v>-7.3311332352</v>
       </c>
       <c r="P55">
-        <v>-22.6263060736</v>
+        <v>-23.2152552448</v>
       </c>
       <c r="Q55">
-        <v>-18.6263060736</v>
+        <v>-19.2152552448</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1718572903175592</v>
+        <v>0.1745976661940279</v>
       </c>
       <c r="T55">
-        <v>2.125507011381276</v>
+        <v>2.171713685541738</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06603126127936657</v>
+        <v>0.06480846014456347</v>
       </c>
       <c r="W55">
-        <v>0.2202298285903254</v>
+        <v>0.2205181650979119</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.275130255330694</v>
+        <v>0.2700352506023478</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1993947356021253</v>
+        <v>0.2012947356021253</v>
       </c>
       <c r="C56">
-        <v>-33.84128456252918</v>
+        <v>-38.63214835305766</v>
       </c>
       <c r="D56">
-        <v>123.1243154374708</v>
+        <v>121.6198516469424</v>
       </c>
       <c r="E56">
-        <v>174.7256</v>
+        <v>178.012</v>
       </c>
       <c r="F56">
-        <v>177.4656</v>
+        <v>180.752</v>
       </c>
       <c r="G56">
         <v>20.5</v>
@@ -5861,37 +5861,37 @@
         <v>11.3</v>
       </c>
       <c r="M56">
-        <v>41.84638848</v>
+        <v>42.6213216</v>
       </c>
       <c r="N56">
-        <v>-30.54638848</v>
+        <v>-31.3213216</v>
       </c>
       <c r="O56">
-        <v>-7.3311332352</v>
+        <v>-7.517117184</v>
       </c>
       <c r="P56">
-        <v>-23.2152552448</v>
+        <v>-23.804204416</v>
       </c>
       <c r="Q56">
-        <v>-19.2152552448</v>
+        <v>-19.804204416</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1745976661940279</v>
+        <v>0.1774598365538952</v>
       </c>
       <c r="T56">
-        <v>2.171713685541738</v>
+        <v>2.219973989664889</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06480846014456347</v>
+        <v>0.06363012450557141</v>
       </c>
       <c r="W56">
-        <v>0.2205181650979119</v>
+        <v>0.2207960166415863</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2700352506023478</v>
+        <v>0.2651255187732142</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2012947356021253</v>
+        <v>0.2031947356021253</v>
       </c>
       <c r="C57">
-        <v>-38.63214835305766</v>
+        <v>-43.38668969365065</v>
       </c>
       <c r="D57">
-        <v>121.6198516469424</v>
+        <v>120.1517103063493</v>
       </c>
       <c r="E57">
-        <v>178.012</v>
+        <v>181.2984</v>
       </c>
       <c r="F57">
-        <v>180.752</v>
+        <v>184.0384</v>
       </c>
       <c r="G57">
         <v>20.5</v>
@@ -5943,37 +5943,37 @@
         <v>11.3</v>
       </c>
       <c r="M57">
-        <v>42.6213216</v>
+        <v>43.39625472</v>
       </c>
       <c r="N57">
-        <v>-31.3213216</v>
+        <v>-32.09625472</v>
       </c>
       <c r="O57">
-        <v>-7.517117184</v>
+        <v>-7.703101132800001</v>
       </c>
       <c r="P57">
-        <v>-23.804204416</v>
+        <v>-24.3931535872</v>
       </c>
       <c r="Q57">
-        <v>-19.804204416</v>
+        <v>-20.3931535872</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1774598365538952</v>
+        <v>0.1804521055664836</v>
       </c>
       <c r="T57">
-        <v>2.219973989664889</v>
+        <v>2.270427943975454</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06363012450557141</v>
+        <v>0.06249387228225763</v>
       </c>
       <c r="W57">
-        <v>0.2207960166415863</v>
+        <v>0.2210639449158437</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2651255187732142</v>
+        <v>0.2603911345094068</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2031947356021253</v>
+        <v>0.2050947356021253</v>
       </c>
       <c r="C58">
-        <v>-43.38668969365065</v>
+        <v>-48.10620830060995</v>
       </c>
       <c r="D58">
-        <v>120.1517103063493</v>
+        <v>118.7185916993901</v>
       </c>
       <c r="E58">
-        <v>181.2984</v>
+        <v>184.5848</v>
       </c>
       <c r="F58">
-        <v>184.0384</v>
+        <v>187.3248</v>
       </c>
       <c r="G58">
         <v>20.5</v>
@@ -6025,37 +6025,37 @@
         <v>11.3</v>
       </c>
       <c r="M58">
-        <v>43.39625472</v>
+        <v>44.17118784</v>
       </c>
       <c r="N58">
-        <v>-32.09625472</v>
+        <v>-32.87118784</v>
       </c>
       <c r="O58">
-        <v>-7.703101132800001</v>
+        <v>-7.889085081600001</v>
       </c>
       <c r="P58">
-        <v>-24.3931535872</v>
+        <v>-24.9821027584</v>
       </c>
       <c r="Q58">
-        <v>-20.3931535872</v>
+        <v>-20.9821027584</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1804521055664836</v>
+        <v>0.1835835498819833</v>
       </c>
       <c r="T58">
-        <v>2.270427943975454</v>
+        <v>2.323228593835348</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06249387228225763</v>
+        <v>0.0613974885580075</v>
       </c>
       <c r="W58">
-        <v>0.2210639449158437</v>
+        <v>0.2213224721980218</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2603911345094068</v>
+        <v>0.2558228689916978</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2050947356021253</v>
+        <v>0.2069947356021253</v>
       </c>
       <c r="C59">
-        <v>-48.10620830060995</v>
+        <v>-52.7919426112887</v>
       </c>
       <c r="D59">
-        <v>118.7185916993901</v>
+        <v>117.3192573887113</v>
       </c>
       <c r="E59">
-        <v>184.5848</v>
+        <v>187.8712</v>
       </c>
       <c r="F59">
-        <v>187.3248</v>
+        <v>190.6112</v>
       </c>
       <c r="G59">
         <v>20.5</v>
@@ -6107,37 +6107,37 @@
         <v>11.3</v>
       </c>
       <c r="M59">
-        <v>44.17118784</v>
+        <v>44.94612096000001</v>
       </c>
       <c r="N59">
-        <v>-32.87118784</v>
+        <v>-33.64612096</v>
       </c>
       <c r="O59">
-        <v>-7.889085081600001</v>
+        <v>-8.075069030400002</v>
       </c>
       <c r="P59">
-        <v>-24.9821027584</v>
+        <v>-25.5710519296</v>
       </c>
       <c r="Q59">
-        <v>-20.9821027584</v>
+        <v>-21.5710519296</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1835835498819833</v>
+        <v>0.1868641105934591</v>
       </c>
       <c r="T59">
-        <v>2.323228593835348</v>
+        <v>2.378543560355238</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0613974885580075</v>
+        <v>0.06033891116907632</v>
       </c>
       <c r="W59">
-        <v>0.2213224721980218</v>
+        <v>0.2215720847463318</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2558228689916978</v>
+        <v>0.2514121298711515</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2069947356021253</v>
+        <v>0.2088947356021252</v>
       </c>
       <c r="C60">
-        <v>-52.79194261128865</v>
+        <v>-57.44507335348956</v>
       </c>
       <c r="D60">
-        <v>117.3192573887113</v>
+        <v>115.9525266465104</v>
       </c>
       <c r="E60">
-        <v>187.8712</v>
+        <v>191.1576</v>
       </c>
       <c r="F60">
-        <v>190.6112</v>
+        <v>193.8976</v>
       </c>
       <c r="G60">
         <v>20.5</v>
@@ -6189,37 +6189,37 @@
         <v>11.3</v>
       </c>
       <c r="M60">
-        <v>44.94612095999999</v>
+        <v>45.72105407999999</v>
       </c>
       <c r="N60">
-        <v>-33.64612095999999</v>
+        <v>-34.42105407999999</v>
       </c>
       <c r="O60">
-        <v>-8.075069030399998</v>
+        <v>-8.261052979199997</v>
       </c>
       <c r="P60">
-        <v>-25.57105192959999</v>
+        <v>-26.1600011008</v>
       </c>
       <c r="Q60">
-        <v>-21.57105192959999</v>
+        <v>-22.1600011008</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1868641105934591</v>
+        <v>0.1903046986567141</v>
       </c>
       <c r="T60">
-        <v>2.378543560355237</v>
+        <v>2.436556817924877</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06033891116907635</v>
+        <v>0.05931621775943098</v>
       </c>
       <c r="W60">
-        <v>0.2215720847463318</v>
+        <v>0.2218132358523262</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2514121298711515</v>
+        <v>0.2471509073309626</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2088947356021252</v>
+        <v>0.2107947356021252</v>
       </c>
       <c r="C61">
-        <v>-57.44507335348956</v>
+        <v>-62.06672686824191</v>
       </c>
       <c r="D61">
-        <v>115.9525266465104</v>
+        <v>114.6172731317581</v>
       </c>
       <c r="E61">
-        <v>191.1576</v>
+        <v>194.444</v>
       </c>
       <c r="F61">
-        <v>193.8976</v>
+        <v>197.184</v>
       </c>
       <c r="G61">
         <v>20.5</v>
@@ -6271,37 +6271,37 @@
         <v>11.3</v>
       </c>
       <c r="M61">
-        <v>45.72105407999999</v>
+        <v>46.4959872</v>
       </c>
       <c r="N61">
-        <v>-34.42105407999999</v>
+        <v>-35.1959872</v>
       </c>
       <c r="O61">
-        <v>-8.261052979199997</v>
+        <v>-8.447036928000001</v>
       </c>
       <c r="P61">
-        <v>-26.1600011008</v>
+        <v>-26.748950272</v>
       </c>
       <c r="Q61">
-        <v>-22.1600011008</v>
+        <v>-22.748950272</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1903046986567141</v>
+        <v>0.193917316123132</v>
       </c>
       <c r="T61">
-        <v>2.436556817924877</v>
+        <v>2.497470738372999</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05931621775943098</v>
+        <v>0.05832761413010713</v>
       </c>
       <c r="W61">
-        <v>0.2218132358523262</v>
+        <v>0.2220463485881208</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2471509073309626</v>
+        <v>0.2430317255421129</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2107947356021252</v>
+        <v>0.2126947356021252</v>
       </c>
       <c r="C62">
-        <v>-62.06672686824191</v>
+        <v>-66.65797820561124</v>
       </c>
       <c r="D62">
-        <v>114.6172731317581</v>
+        <v>113.3124217943887</v>
       </c>
       <c r="E62">
-        <v>194.444</v>
+        <v>197.7304</v>
       </c>
       <c r="F62">
-        <v>197.184</v>
+        <v>200.4704</v>
       </c>
       <c r="G62">
         <v>20.5</v>
@@ -6353,37 +6353,37 @@
         <v>11.3</v>
       </c>
       <c r="M62">
-        <v>46.4959872</v>
+        <v>47.27092031999999</v>
       </c>
       <c r="N62">
-        <v>-35.1959872</v>
+        <v>-35.97092031999999</v>
       </c>
       <c r="O62">
-        <v>-8.447036928000001</v>
+        <v>-8.633020876799998</v>
       </c>
       <c r="P62">
-        <v>-26.748950272</v>
+        <v>-27.33789944319999</v>
       </c>
       <c r="Q62">
-        <v>-22.748950272</v>
+        <v>-23.33789944319999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.193917316123132</v>
+        <v>0.1977151960237251</v>
       </c>
       <c r="T62">
-        <v>2.497470738372999</v>
+        <v>2.561508449613332</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05832761413010713</v>
+        <v>0.05737142373453161</v>
       </c>
       <c r="W62">
-        <v>0.2220463485881208</v>
+        <v>0.2222718182833975</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2430317255421129</v>
+        <v>0.2390475988938818</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2126947356021252</v>
+        <v>0.2145947356021252</v>
       </c>
       <c r="C63">
-        <v>-66.65797820561124</v>
+        <v>-71.21985401142558</v>
       </c>
       <c r="D63">
-        <v>113.3124217943887</v>
+        <v>112.0369459885744</v>
       </c>
       <c r="E63">
-        <v>197.7304</v>
+        <v>201.0168</v>
       </c>
       <c r="F63">
-        <v>200.4704</v>
+        <v>203.7568</v>
       </c>
       <c r="G63">
         <v>20.5</v>
@@ -6435,37 +6435,37 @@
         <v>11.3</v>
       </c>
       <c r="M63">
-        <v>47.27092031999999</v>
+        <v>48.04585344</v>
       </c>
       <c r="N63">
-        <v>-35.97092031999999</v>
+        <v>-36.74585344</v>
       </c>
       <c r="O63">
-        <v>-8.633020876799998</v>
+        <v>-8.8190048256</v>
       </c>
       <c r="P63">
-        <v>-27.33789944319999</v>
+        <v>-27.9268486144</v>
       </c>
       <c r="Q63">
-        <v>-23.33789944319999</v>
+        <v>-23.9268486144</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1977151960237251</v>
+        <v>0.2017129643401389</v>
       </c>
       <c r="T63">
-        <v>2.561508449613332</v>
+        <v>2.62891656670842</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05737142373453161</v>
+        <v>0.05644607819042625</v>
       </c>
       <c r="W63">
-        <v>0.2222718182833975</v>
+        <v>0.2224900147626975</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2390475988938818</v>
+        <v>0.2351919924601094</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2145947356021252</v>
+        <v>0.2164947356021252</v>
       </c>
       <c r="C64">
-        <v>-71.21985401142558</v>
+        <v>-75.75333522120857</v>
       </c>
       <c r="D64">
-        <v>112.0369459885744</v>
+        <v>110.7898647787914</v>
       </c>
       <c r="E64">
-        <v>201.0168</v>
+        <v>204.3032</v>
       </c>
       <c r="F64">
-        <v>203.7568</v>
+        <v>207.0432</v>
       </c>
       <c r="G64">
         <v>20.5</v>
@@ -6517,37 +6517,37 @@
         <v>11.3</v>
       </c>
       <c r="M64">
-        <v>48.04585344</v>
+        <v>48.82078655999999</v>
       </c>
       <c r="N64">
-        <v>-36.74585344</v>
+        <v>-37.52078655999999</v>
       </c>
       <c r="O64">
-        <v>-8.8190048256</v>
+        <v>-9.004988774399997</v>
       </c>
       <c r="P64">
-        <v>-27.9268486144</v>
+        <v>-28.51579778559999</v>
       </c>
       <c r="Q64">
-        <v>-23.9268486144</v>
+        <v>-24.51579778559999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2017129643401389</v>
+        <v>0.2059268282412238</v>
       </c>
       <c r="T64">
-        <v>2.62891656670842</v>
+        <v>2.699968365808648</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05644607819042625</v>
+        <v>0.05555010869534013</v>
       </c>
       <c r="W64">
-        <v>0.2224900147626975</v>
+        <v>0.2227012843696388</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2351919924601094</v>
+        <v>0.2314587862305839</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2164947356021252</v>
+        <v>0.2183947356021252</v>
       </c>
       <c r="C65">
-        <v>-75.75333522120857</v>
+        <v>-80.25935957617716</v>
       </c>
       <c r="D65">
-        <v>110.7898647787914</v>
+        <v>109.5702404238229</v>
       </c>
       <c r="E65">
-        <v>204.3032</v>
+        <v>207.5896</v>
       </c>
       <c r="F65">
-        <v>207.0432</v>
+        <v>210.3296</v>
       </c>
       <c r="G65">
         <v>20.5</v>
@@ -6599,37 +6599,37 @@
         <v>11.3</v>
       </c>
       <c r="M65">
-        <v>48.82078655999999</v>
+        <v>49.59571968</v>
       </c>
       <c r="N65">
-        <v>-37.52078655999999</v>
+        <v>-38.29571968</v>
       </c>
       <c r="O65">
-        <v>-9.004988774399997</v>
+        <v>-9.190972723200002</v>
       </c>
       <c r="P65">
-        <v>-28.51579778559999</v>
+        <v>-29.1047469568</v>
       </c>
       <c r="Q65">
-        <v>-24.51579778559999</v>
+        <v>-25.1047469568</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2059268282412238</v>
+        <v>0.2103747956923689</v>
       </c>
       <c r="T65">
-        <v>2.699968365808648</v>
+        <v>2.77496748708111</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05555010869534013</v>
+        <v>0.05468213824697543</v>
       </c>
       <c r="W65">
-        <v>0.2227012843696388</v>
+        <v>0.2229059518013632</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2314587862305839</v>
+        <v>0.2278422426957308</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2183947356021252</v>
+        <v>0.2202947356021253</v>
       </c>
       <c r="C66">
-        <v>-80.25935957617716</v>
+        <v>-84.73882397486449</v>
       </c>
       <c r="D66">
-        <v>109.5702404238229</v>
+        <v>108.3771760251355</v>
       </c>
       <c r="E66">
-        <v>207.5896</v>
+        <v>210.876</v>
       </c>
       <c r="F66">
-        <v>210.3296</v>
+        <v>213.616</v>
       </c>
       <c r="G66">
         <v>20.5</v>
@@ -6681,37 +6681,37 @@
         <v>11.3</v>
       </c>
       <c r="M66">
-        <v>49.59571968</v>
+        <v>50.3706528</v>
       </c>
       <c r="N66">
-        <v>-38.29571968</v>
+        <v>-39.0706528</v>
       </c>
       <c r="O66">
-        <v>-9.190972723200002</v>
+        <v>-9.376956672</v>
       </c>
       <c r="P66">
-        <v>-29.1047469568</v>
+        <v>-29.69369612800001</v>
       </c>
       <c r="Q66">
-        <v>-25.1047469568</v>
+        <v>-25.69369612800001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2103747956923689</v>
+        <v>0.2150769327121509</v>
       </c>
       <c r="T66">
-        <v>2.77496748708111</v>
+        <v>2.854252272426285</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05468213824697543</v>
+        <v>0.05384087458163735</v>
       </c>
       <c r="W66">
-        <v>0.2229059518013632</v>
+        <v>0.2231043217736499</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2278422426957308</v>
+        <v>0.2243369774234889</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2202947356021253</v>
+        <v>0.2221947356021253</v>
       </c>
       <c r="C67">
-        <v>-84.73882397486449</v>
+        <v>-89.19258667276398</v>
       </c>
       <c r="D67">
-        <v>108.3771760251355</v>
+        <v>107.209813327236</v>
       </c>
       <c r="E67">
-        <v>210.876</v>
+        <v>214.1624</v>
       </c>
       <c r="F67">
-        <v>213.616</v>
+        <v>216.9024</v>
       </c>
       <c r="G67">
         <v>20.5</v>
@@ -6763,37 +6763,37 @@
         <v>11.3</v>
       </c>
       <c r="M67">
-        <v>50.3706528</v>
+        <v>51.14558592</v>
       </c>
       <c r="N67">
-        <v>-39.0706528</v>
+        <v>-39.84558592</v>
       </c>
       <c r="O67">
-        <v>-9.376956672</v>
+        <v>-9.562940620800001</v>
       </c>
       <c r="P67">
-        <v>-29.69369612800001</v>
+        <v>-30.28264529920001</v>
       </c>
       <c r="Q67">
-        <v>-25.69369612800001</v>
+        <v>-26.28264529920001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2150769327121509</v>
+        <v>0.2200556660272141</v>
       </c>
       <c r="T67">
-        <v>2.854252272426285</v>
+        <v>2.938200868674116</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05384087458163735</v>
+        <v>0.05302510375464284</v>
       </c>
       <c r="W67">
-        <v>0.2231043217736499</v>
+        <v>0.2232966805346552</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2243369774234889</v>
+        <v>0.2209379323110118</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2221947356021253</v>
+        <v>0.2240947356021253</v>
       </c>
       <c r="C68">
-        <v>-89.19258667276398</v>
+        <v>-93.62146934132871</v>
       </c>
       <c r="D68">
-        <v>107.209813327236</v>
+        <v>106.0673306586713</v>
       </c>
       <c r="E68">
-        <v>214.1624</v>
+        <v>217.4488</v>
       </c>
       <c r="F68">
-        <v>216.9024</v>
+        <v>220.1888</v>
       </c>
       <c r="G68">
         <v>20.5</v>
@@ -6845,37 +6845,37 @@
         <v>11.3</v>
       </c>
       <c r="M68">
-        <v>51.14558592</v>
+        <v>51.92051904</v>
       </c>
       <c r="N68">
-        <v>-39.84558592</v>
+        <v>-40.62051904</v>
       </c>
       <c r="O68">
-        <v>-9.562940620800001</v>
+        <v>-9.748924569600002</v>
       </c>
       <c r="P68">
-        <v>-30.28264529920001</v>
+        <v>-30.87159447040001</v>
       </c>
       <c r="Q68">
-        <v>-26.28264529920001</v>
+        <v>-26.87159447040001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2200556660272141</v>
+        <v>0.2253361407553116</v>
       </c>
       <c r="T68">
-        <v>2.938200868674116</v>
+        <v>3.027237258633939</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05302510375464284</v>
+        <v>0.05223368429561832</v>
       </c>
       <c r="W68">
-        <v>0.2232966805346552</v>
+        <v>0.2234832972430932</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2209379323110118</v>
+        <v>0.217640351231743</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2240947356021253</v>
+        <v>0.2259947356021253</v>
       </c>
       <c r="C69">
-        <v>-93.62146934132871</v>
+        <v>-98.02625899670937</v>
       </c>
       <c r="D69">
-        <v>106.0673306586713</v>
+        <v>104.9489410032906</v>
       </c>
       <c r="E69">
-        <v>217.4488</v>
+        <v>220.7352</v>
       </c>
       <c r="F69">
-        <v>220.1888</v>
+        <v>223.4752</v>
       </c>
       <c r="G69">
         <v>20.5</v>
@@ -6927,37 +6927,37 @@
         <v>11.3</v>
       </c>
       <c r="M69">
-        <v>51.92051904</v>
+        <v>52.69545216</v>
       </c>
       <c r="N69">
-        <v>-40.62051904</v>
+        <v>-41.39545216</v>
       </c>
       <c r="O69">
-        <v>-9.748924569600002</v>
+        <v>-9.9349085184</v>
       </c>
       <c r="P69">
-        <v>-30.87159447040001</v>
+        <v>-31.4605436416</v>
       </c>
       <c r="Q69">
-        <v>-26.87159447040001</v>
+        <v>-27.4605436416</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2253361407553116</v>
+        <v>0.2309466451539151</v>
       </c>
       <c r="T69">
-        <v>3.027237258633939</v>
+        <v>3.121838422966249</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05223368429561832</v>
+        <v>0.05146554187950628</v>
       </c>
       <c r="W69">
-        <v>0.2234832972430932</v>
+        <v>0.2236644252248124</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.217640351231743</v>
+        <v>0.2144397578312761</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2259947356021253</v>
+        <v>0.2278947356021253</v>
       </c>
       <c r="C70">
-        <v>-98.02625899670937</v>
+        <v>-102.4077098077441</v>
       </c>
       <c r="D70">
-        <v>104.9489410032906</v>
+        <v>103.8538901922559</v>
       </c>
       <c r="E70">
-        <v>220.7352</v>
+        <v>224.0216</v>
       </c>
       <c r="F70">
-        <v>223.4752</v>
+        <v>226.7616</v>
       </c>
       <c r="G70">
         <v>20.5</v>
@@ -7009,37 +7009,37 @@
         <v>11.3</v>
       </c>
       <c r="M70">
-        <v>52.69545216</v>
+        <v>53.47038528000001</v>
       </c>
       <c r="N70">
-        <v>-41.39545216</v>
+        <v>-42.17038528</v>
       </c>
       <c r="O70">
-        <v>-9.9349085184</v>
+        <v>-10.1208924672</v>
       </c>
       <c r="P70">
-        <v>-31.4605436416</v>
+        <v>-32.0494928128</v>
       </c>
       <c r="Q70">
-        <v>-27.4605436416</v>
+        <v>-28.0494928128</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2309466451539151</v>
+        <v>0.2369191175782349</v>
       </c>
       <c r="T70">
-        <v>3.121838422966249</v>
+        <v>3.222542888223225</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05146554187950628</v>
+        <v>0.05071966446096271</v>
       </c>
       <c r="W70">
-        <v>0.2236644252248124</v>
+        <v>0.223840303120105</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2144397578312761</v>
+        <v>0.2113319352540114</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2278947356021253</v>
+        <v>0.2297947356021253</v>
       </c>
       <c r="C71">
-        <v>-102.4077098077441</v>
+        <v>-106.7665447919274</v>
       </c>
       <c r="D71">
-        <v>103.8538901922559</v>
+        <v>102.7814552080726</v>
       </c>
       <c r="E71">
-        <v>224.0216</v>
+        <v>227.308</v>
       </c>
       <c r="F71">
-        <v>226.7616</v>
+        <v>230.048</v>
       </c>
       <c r="G71">
         <v>20.5</v>
@@ -7091,37 +7091,37 @@
         <v>11.3</v>
       </c>
       <c r="M71">
-        <v>53.47038528000001</v>
+        <v>54.2453184</v>
       </c>
       <c r="N71">
-        <v>-42.17038528</v>
+        <v>-42.9453184</v>
       </c>
       <c r="O71">
-        <v>-10.1208924672</v>
+        <v>-10.306876416</v>
       </c>
       <c r="P71">
-        <v>-32.0494928128</v>
+        <v>-32.638441984</v>
       </c>
       <c r="Q71">
-        <v>-28.0494928128</v>
+        <v>-28.638441984</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2369191175782349</v>
+        <v>0.2432897548308427</v>
       </c>
       <c r="T71">
-        <v>3.222542888223225</v>
+        <v>3.329960984497332</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05071966446096271</v>
+        <v>0.04999509782580611</v>
       </c>
       <c r="W71">
-        <v>0.223840303120105</v>
+        <v>0.2240111559326749</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2113319352540114</v>
+        <v>0.2083129076075254</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2297947356021253</v>
+        <v>0.2316947356021253</v>
       </c>
       <c r="C72">
-        <v>-106.7665447919274</v>
+        <v>-111.103457407375</v>
       </c>
       <c r="D72">
-        <v>102.7814552080726</v>
+        <v>101.730942592625</v>
       </c>
       <c r="E72">
-        <v>227.308</v>
+        <v>230.5944</v>
       </c>
       <c r="F72">
-        <v>230.048</v>
+        <v>233.3344</v>
       </c>
       <c r="G72">
         <v>20.5</v>
@@ -7173,37 +7173,37 @@
         <v>11.3</v>
       </c>
       <c r="M72">
-        <v>54.2453184</v>
+        <v>55.02025152000001</v>
       </c>
       <c r="N72">
-        <v>-42.9453184</v>
+        <v>-43.72025152000001</v>
       </c>
       <c r="O72">
-        <v>-10.306876416</v>
+        <v>-10.4928603648</v>
       </c>
       <c r="P72">
-        <v>-32.638441984</v>
+        <v>-33.2273911552</v>
       </c>
       <c r="Q72">
-        <v>-28.638441984</v>
+        <v>-29.2273911552</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2432897548308427</v>
+        <v>0.2500997463767338</v>
       </c>
       <c r="T72">
-        <v>3.329960984497332</v>
+        <v>3.444787225342068</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04999509782580611</v>
+        <v>0.04929094151840038</v>
       </c>
       <c r="W72">
-        <v>0.2240111559326749</v>
+        <v>0.2241771959899612</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2083129076075254</v>
+        <v>0.2053789229933349</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2316947356021252</v>
+        <v>0.2335947356021252</v>
       </c>
       <c r="C73">
-        <v>-111.103457407375</v>
+        <v>-115.4191130481481</v>
       </c>
       <c r="D73">
-        <v>101.730942592625</v>
+        <v>100.7016869518518</v>
       </c>
       <c r="E73">
-        <v>230.5944</v>
+        <v>233.8808</v>
       </c>
       <c r="F73">
-        <v>233.3344</v>
+        <v>236.6208</v>
       </c>
       <c r="G73">
         <v>20.5</v>
@@ -7255,37 +7255,37 @@
         <v>11.3</v>
       </c>
       <c r="M73">
-        <v>55.02025152</v>
+        <v>55.79518464</v>
       </c>
       <c r="N73">
-        <v>-43.72025152000001</v>
+        <v>-44.49518463999999</v>
       </c>
       <c r="O73">
-        <v>-10.4928603648</v>
+        <v>-10.6788443136</v>
       </c>
       <c r="P73">
-        <v>-33.2273911552</v>
+        <v>-33.8163403264</v>
       </c>
       <c r="Q73">
-        <v>-29.2273911552</v>
+        <v>-29.8163403264</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2500997463767338</v>
+        <v>0.2573961658901885</v>
       </c>
       <c r="T73">
-        <v>3.444787225342067</v>
+        <v>3.567815340532855</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04929094151840039</v>
+        <v>0.04860634510842261</v>
       </c>
       <c r="W73">
-        <v>0.2241771959899612</v>
+        <v>0.2243386238234339</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2053789229933349</v>
+        <v>0.202526437951761</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2335947356021252</v>
+        <v>0.2354947356021252</v>
       </c>
       <c r="C74">
-        <v>-115.4191130481481</v>
+        <v>-119.7141504497144</v>
       </c>
       <c r="D74">
-        <v>100.7016869518518</v>
+        <v>99.69304955028559</v>
       </c>
       <c r="E74">
-        <v>233.8808</v>
+        <v>237.1672</v>
       </c>
       <c r="F74">
-        <v>236.6208</v>
+        <v>239.9072</v>
       </c>
       <c r="G74">
         <v>20.5</v>
@@ -7337,37 +7337,37 @@
         <v>11.3</v>
       </c>
       <c r="M74">
-        <v>55.79518464</v>
+        <v>56.57011776</v>
       </c>
       <c r="N74">
-        <v>-44.49518463999999</v>
+        <v>-45.27011776000001</v>
       </c>
       <c r="O74">
-        <v>-10.6788443136</v>
+        <v>-10.8648282624</v>
       </c>
       <c r="P74">
-        <v>-33.8163403264</v>
+        <v>-34.4052894976</v>
       </c>
       <c r="Q74">
-        <v>-29.8163403264</v>
+        <v>-30.4052894976</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2573961658901885</v>
+        <v>0.2652330609231585</v>
       </c>
       <c r="T74">
-        <v>3.567815340532855</v>
+        <v>3.69995664944148</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04860634510842261</v>
+        <v>0.04794050476447161</v>
       </c>
       <c r="W74">
-        <v>0.2243386238234339</v>
+        <v>0.2244956289765376</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.202526437951761</v>
+        <v>0.1997521031852983</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2354947356021252</v>
+        <v>0.2373947356021253</v>
       </c>
       <c r="C75">
-        <v>-119.7141504497144</v>
+        <v>-123.9891830107828</v>
       </c>
       <c r="D75">
-        <v>99.69304955028559</v>
+        <v>98.70441698921722</v>
       </c>
       <c r="E75">
-        <v>237.1672</v>
+        <v>240.4536</v>
       </c>
       <c r="F75">
-        <v>239.9072</v>
+        <v>243.1936</v>
       </c>
       <c r="G75">
         <v>20.5</v>
@@ -7419,37 +7419,37 @@
         <v>11.3</v>
       </c>
       <c r="M75">
-        <v>56.57011776</v>
+        <v>57.34505088</v>
       </c>
       <c r="N75">
-        <v>-45.27011776000001</v>
+        <v>-46.04505087999999</v>
       </c>
       <c r="O75">
-        <v>-10.8648282624</v>
+        <v>-11.0508122112</v>
       </c>
       <c r="P75">
-        <v>-34.4052894976</v>
+        <v>-34.99423866879999</v>
       </c>
       <c r="Q75">
-        <v>-30.4052894976</v>
+        <v>-30.99423866879999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2652330609231585</v>
+        <v>0.2736727940355877</v>
       </c>
       <c r="T75">
-        <v>3.69995664944148</v>
+        <v>3.842262674419998</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04794050476447161</v>
+        <v>0.04729266010549227</v>
       </c>
       <c r="W75">
-        <v>0.2244956289765376</v>
+        <v>0.2246483907471249</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1997521031852983</v>
+        <v>0.1970527504395512</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2373947356021253</v>
+        <v>0.2392947356021252</v>
       </c>
       <c r="C76">
-        <v>-123.9891830107828</v>
+        <v>-128.2448000372611</v>
       </c>
       <c r="D76">
-        <v>98.70441698921722</v>
+        <v>97.73519996273889</v>
       </c>
       <c r="E76">
-        <v>240.4536</v>
+        <v>243.74</v>
       </c>
       <c r="F76">
-        <v>243.1936</v>
+        <v>246.48</v>
       </c>
       <c r="G76">
         <v>20.5</v>
@@ -7501,37 +7501,37 @@
         <v>11.3</v>
       </c>
       <c r="M76">
-        <v>57.34505088</v>
+        <v>58.119984</v>
       </c>
       <c r="N76">
-        <v>-46.04505087999999</v>
+        <v>-46.81998400000001</v>
       </c>
       <c r="O76">
-        <v>-11.0508122112</v>
+        <v>-11.23679616</v>
       </c>
       <c r="P76">
-        <v>-34.99423866879999</v>
+        <v>-35.58318784000001</v>
       </c>
       <c r="Q76">
-        <v>-30.99423866879999</v>
+        <v>-31.58318784000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2736727940355877</v>
+        <v>0.2827877057970112</v>
       </c>
       <c r="T76">
-        <v>3.842262674419998</v>
+        <v>3.995953181396798</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04729266010549227</v>
+        <v>0.0466620913040857</v>
       </c>
       <c r="W76">
-        <v>0.2246483907471249</v>
+        <v>0.2247970788704966</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1970527504395512</v>
+        <v>0.1944253804336904</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2392947356021252</v>
+        <v>0.2411947356021253</v>
       </c>
       <c r="C77">
-        <v>-128.2448000372611</v>
+        <v>-132.4815679136369</v>
       </c>
       <c r="D77">
-        <v>97.73519996273889</v>
+        <v>96.78483208636311</v>
       </c>
       <c r="E77">
-        <v>243.74</v>
+        <v>247.0264</v>
       </c>
       <c r="F77">
-        <v>246.48</v>
+        <v>249.7664</v>
       </c>
       <c r="G77">
         <v>20.5</v>
@@ -7583,37 +7583,37 @@
         <v>11.3</v>
       </c>
       <c r="M77">
-        <v>58.119984</v>
+        <v>58.89491712</v>
       </c>
       <c r="N77">
-        <v>-46.81998400000001</v>
+        <v>-47.59491712000001</v>
       </c>
       <c r="O77">
-        <v>-11.23679616</v>
+        <v>-11.4227801088</v>
       </c>
       <c r="P77">
-        <v>-35.58318784000001</v>
+        <v>-36.17213701120001</v>
       </c>
       <c r="Q77">
-        <v>-31.58318784000001</v>
+        <v>-32.17213701120001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2827877057970112</v>
+        <v>0.2926621935385534</v>
       </c>
       <c r="T77">
-        <v>3.995953181396798</v>
+        <v>4.162451230621666</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0466620913040857</v>
+        <v>0.04604811641850563</v>
       </c>
       <c r="W77">
-        <v>0.2247970788704966</v>
+        <v>0.2249418541485164</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1944253804336904</v>
+        <v>0.1918671517437733</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2411947356021253</v>
+        <v>0.2430947356021252</v>
       </c>
       <c r="C78">
-        <v>-132.4815679136369</v>
+        <v>-136.7000312066735</v>
       </c>
       <c r="D78">
-        <v>96.78483208636311</v>
+        <v>95.8527687933265</v>
       </c>
       <c r="E78">
-        <v>247.0264</v>
+        <v>250.3128</v>
       </c>
       <c r="F78">
-        <v>249.7664</v>
+        <v>253.0528</v>
       </c>
       <c r="G78">
         <v>20.5</v>
@@ -7665,37 +7665,37 @@
         <v>11.3</v>
       </c>
       <c r="M78">
-        <v>58.89491712</v>
+        <v>59.66985024</v>
       </c>
       <c r="N78">
-        <v>-47.59491712000001</v>
+        <v>-48.36985024000001</v>
       </c>
       <c r="O78">
-        <v>-11.4227801088</v>
+        <v>-11.6087640576</v>
       </c>
       <c r="P78">
-        <v>-36.17213701120001</v>
+        <v>-36.76108618240001</v>
       </c>
       <c r="Q78">
-        <v>-32.17213701120001</v>
+        <v>-32.76108618240001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2926621935385534</v>
+        <v>0.3033953323880557</v>
       </c>
       <c r="T78">
-        <v>4.162451230621666</v>
+        <v>4.343427371083477</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04604811641850563</v>
+        <v>0.04545008893255101</v>
       </c>
       <c r="W78">
-        <v>0.2249418541485164</v>
+        <v>0.2250828690297045</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1918671517437733</v>
+        <v>0.1893753705522958</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2430947356021252</v>
+        <v>0.2449947356021253</v>
       </c>
       <c r="C79">
-        <v>-136.7000312066735</v>
+        <v>-140.9007137059414</v>
       </c>
       <c r="D79">
-        <v>95.8527687933265</v>
+        <v>94.93848629405861</v>
       </c>
       <c r="E79">
-        <v>250.3128</v>
+        <v>253.5992</v>
       </c>
       <c r="F79">
-        <v>253.0528</v>
+        <v>256.3392</v>
       </c>
       <c r="G79">
         <v>20.5</v>
@@ -7747,37 +7747,37 @@
         <v>11.3</v>
       </c>
       <c r="M79">
-        <v>59.66985024</v>
+        <v>60.44478336</v>
       </c>
       <c r="N79">
-        <v>-48.36985024000001</v>
+        <v>-49.14478336000001</v>
       </c>
       <c r="O79">
-        <v>-11.6087640576</v>
+        <v>-11.7947480064</v>
       </c>
       <c r="P79">
-        <v>-36.76108618240001</v>
+        <v>-37.35003535360001</v>
       </c>
       <c r="Q79">
-        <v>-32.76108618240001</v>
+        <v>-33.35003535360001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3033953323880557</v>
+        <v>0.3151042111329673</v>
       </c>
       <c r="T79">
-        <v>4.343427371083477</v>
+        <v>4.540855887950907</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04545008893255101</v>
+        <v>0.04486739548469779</v>
       </c>
       <c r="W79">
-        <v>0.2250828690297045</v>
+        <v>0.2252202681447083</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1893753705522958</v>
+        <v>0.1869474811862407</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2449947356021253</v>
+        <v>0.2468947356021253</v>
       </c>
       <c r="C80">
-        <v>-140.9007137059414</v>
+        <v>-145.0841194053627</v>
       </c>
       <c r="D80">
-        <v>94.93848629405861</v>
+        <v>94.04148059463736</v>
       </c>
       <c r="E80">
-        <v>253.5992</v>
+        <v>256.8856</v>
       </c>
       <c r="F80">
-        <v>256.3392</v>
+        <v>259.6256</v>
       </c>
       <c r="G80">
         <v>20.5</v>
@@ -7829,37 +7829,37 @@
         <v>11.3</v>
       </c>
       <c r="M80">
-        <v>60.44478336</v>
+        <v>61.21971648000001</v>
       </c>
       <c r="N80">
-        <v>-49.14478336000001</v>
+        <v>-49.91971648000001</v>
       </c>
       <c r="O80">
-        <v>-11.7947480064</v>
+        <v>-11.9807319552</v>
       </c>
       <c r="P80">
-        <v>-37.35003535360001</v>
+        <v>-37.93898452480001</v>
       </c>
       <c r="Q80">
-        <v>-33.35003535360001</v>
+        <v>-33.93898452480001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3151042111329673</v>
+        <v>0.3279282211869182</v>
       </c>
       <c r="T80">
-        <v>4.540855887950907</v>
+        <v>4.757087120710476</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04486739548469779</v>
+        <v>0.04429945376970161</v>
       </c>
       <c r="W80">
-        <v>0.2252202681447083</v>
+        <v>0.2253541888011044</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1869474811862407</v>
+        <v>0.1845810573737567</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2468947356021253</v>
+        <v>0.2487947356021252</v>
       </c>
       <c r="C81">
-        <v>-145.0841194053627</v>
+        <v>-149.2507334296318</v>
       </c>
       <c r="D81">
-        <v>94.04148059463736</v>
+        <v>93.16126657036817</v>
       </c>
       <c r="E81">
-        <v>256.8856</v>
+        <v>260.172</v>
       </c>
       <c r="F81">
-        <v>259.6256</v>
+        <v>262.912</v>
       </c>
       <c r="G81">
         <v>20.5</v>
@@ -7911,37 +7911,37 @@
         <v>11.3</v>
       </c>
       <c r="M81">
-        <v>61.21971648000001</v>
+        <v>61.9946496</v>
       </c>
       <c r="N81">
-        <v>-49.91971648000001</v>
+        <v>-50.69464959999999</v>
       </c>
       <c r="O81">
-        <v>-11.9807319552</v>
+        <v>-12.166715904</v>
       </c>
       <c r="P81">
-        <v>-37.93898452480001</v>
+        <v>-38.52793369599999</v>
       </c>
       <c r="Q81">
-        <v>-33.93898452480001</v>
+        <v>-34.52793369599999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3279282211869182</v>
+        <v>0.342034632246264</v>
       </c>
       <c r="T81">
-        <v>4.757087120710476</v>
+        <v>4.994941476745998</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04429945376970161</v>
+        <v>0.04374571059758035</v>
       </c>
       <c r="W81">
-        <v>0.2253541888011044</v>
+        <v>0.2254847614410906</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1845810573737567</v>
+        <v>0.1822737941565848</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2487947356021252</v>
+        <v>0.2506947356021253</v>
       </c>
       <c r="C82">
-        <v>-149.2507334296318</v>
+        <v>-153.4010229090932</v>
       </c>
       <c r="D82">
-        <v>93.16126657036817</v>
+        <v>92.29737709090676</v>
       </c>
       <c r="E82">
-        <v>260.172</v>
+        <v>263.4584</v>
       </c>
       <c r="F82">
-        <v>262.912</v>
+        <v>266.1984</v>
       </c>
       <c r="G82">
         <v>20.5</v>
@@ -7993,37 +7993,37 @@
         <v>11.3</v>
       </c>
       <c r="M82">
-        <v>61.9946496</v>
+        <v>62.76958272</v>
       </c>
       <c r="N82">
-        <v>-50.69464959999999</v>
+        <v>-51.46958272000001</v>
       </c>
       <c r="O82">
-        <v>-12.166715904</v>
+        <v>-12.3526998528</v>
       </c>
       <c r="P82">
-        <v>-38.52793369599999</v>
+        <v>-39.1168828672</v>
       </c>
       <c r="Q82">
-        <v>-34.52793369599999</v>
+        <v>-35.1168828672</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.342034632246264</v>
+        <v>0.357625928680278</v>
       </c>
       <c r="T82">
-        <v>4.994941476745998</v>
+        <v>5.257833133416842</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04374571059758035</v>
+        <v>0.04320564009637565</v>
       </c>
       <c r="W82">
-        <v>0.2254847614410906</v>
+        <v>0.2256121100652747</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1822737941565848</v>
+        <v>0.1800235004015651</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2506947356021253</v>
+        <v>0.2525947356021253</v>
       </c>
       <c r="C83">
-        <v>-153.4010229090932</v>
+        <v>-157.535437806388</v>
       </c>
       <c r="D83">
-        <v>92.29737709090676</v>
+        <v>91.44936219361206</v>
       </c>
       <c r="E83">
-        <v>263.4584</v>
+        <v>266.7448</v>
       </c>
       <c r="F83">
-        <v>266.1984</v>
+        <v>269.4848</v>
       </c>
       <c r="G83">
         <v>20.5</v>
@@ -8075,37 +8075,37 @@
         <v>11.3</v>
       </c>
       <c r="M83">
-        <v>62.76958272</v>
+        <v>63.54451584</v>
       </c>
       <c r="N83">
-        <v>-51.46958272000001</v>
+        <v>-52.24451584000001</v>
       </c>
       <c r="O83">
-        <v>-12.3526998528</v>
+        <v>-12.5386838016</v>
       </c>
       <c r="P83">
-        <v>-39.1168828672</v>
+        <v>-39.7058320384</v>
       </c>
       <c r="Q83">
-        <v>-35.1168828672</v>
+        <v>-35.7058320384</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.357625928680278</v>
+        <v>0.3749495913847379</v>
       </c>
       <c r="T83">
-        <v>5.257833133416842</v>
+        <v>5.549934974162221</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04320564009637565</v>
+        <v>0.04267874204641985</v>
       </c>
       <c r="W83">
-        <v>0.2256121100652747</v>
+        <v>0.2257363526254542</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1800235004015651</v>
+        <v>0.1778280918600826</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2525947356021253</v>
+        <v>0.2544947356021253</v>
       </c>
       <c r="C84">
-        <v>-157.535437806388</v>
+        <v>-161.6544116979456</v>
       </c>
       <c r="D84">
-        <v>91.44936219361206</v>
+        <v>90.61678830205439</v>
       </c>
       <c r="E84">
-        <v>266.7448</v>
+        <v>270.0312</v>
       </c>
       <c r="F84">
-        <v>269.4848</v>
+        <v>272.7712</v>
       </c>
       <c r="G84">
         <v>20.5</v>
@@ -8157,37 +8157,37 @@
         <v>11.3</v>
       </c>
       <c r="M84">
-        <v>63.54451584</v>
+        <v>64.31944896</v>
       </c>
       <c r="N84">
-        <v>-52.24451584000001</v>
+        <v>-53.01944896000001</v>
       </c>
       <c r="O84">
-        <v>-12.5386838016</v>
+        <v>-12.7246677504</v>
       </c>
       <c r="P84">
-        <v>-39.7058320384</v>
+        <v>-40.2947812096</v>
       </c>
       <c r="Q84">
-        <v>-35.7058320384</v>
+        <v>-36.2947812096</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3749495913847379</v>
+        <v>0.3943113320544284</v>
       </c>
       <c r="T84">
-        <v>5.549934974162221</v>
+        <v>5.876401737348235</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04267874204641985</v>
+        <v>0.0421645403350172</v>
       </c>
       <c r="W84">
-        <v>0.2257363526254542</v>
+        <v>0.225857601389003</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1778280918600826</v>
+        <v>0.1756855847292382</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2544947356021253</v>
+        <v>0.2563947356021253</v>
       </c>
       <c r="C85">
-        <v>-161.6544116979456</v>
+        <v>-165.7583625131721</v>
       </c>
       <c r="D85">
-        <v>90.61678830205439</v>
+        <v>89.79923748682798</v>
       </c>
       <c r="E85">
-        <v>270.0312</v>
+        <v>273.3176</v>
       </c>
       <c r="F85">
-        <v>272.7712</v>
+        <v>276.0576</v>
       </c>
       <c r="G85">
         <v>20.5</v>
@@ -8239,37 +8239,37 @@
         <v>11.3</v>
       </c>
       <c r="M85">
-        <v>64.31944896</v>
+        <v>65.09438208000002</v>
       </c>
       <c r="N85">
-        <v>-53.01944896000001</v>
+        <v>-53.79438208000002</v>
       </c>
       <c r="O85">
-        <v>-12.7246677504</v>
+        <v>-12.9106516992</v>
       </c>
       <c r="P85">
-        <v>-40.2947812096</v>
+        <v>-40.88373038080002</v>
       </c>
       <c r="Q85">
-        <v>-36.2947812096</v>
+        <v>-36.88373038080002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3943113320544284</v>
+        <v>0.4160932903078303</v>
       </c>
       <c r="T85">
-        <v>5.876401737348235</v>
+        <v>6.243676845932502</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0421645403350172</v>
+        <v>0.04166258152150508</v>
       </c>
       <c r="W85">
-        <v>0.225857601389003</v>
+        <v>0.2259759632772291</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1756855847292382</v>
+        <v>0.1735940896729378</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2563947356021253</v>
+        <v>0.2582947356021252</v>
       </c>
       <c r="C86">
-        <v>-165.758362513172</v>
+        <v>-169.8476932339802</v>
       </c>
       <c r="D86">
-        <v>89.79923748682798</v>
+        <v>88.99630676601977</v>
       </c>
       <c r="E86">
-        <v>273.3176</v>
+        <v>276.604</v>
       </c>
       <c r="F86">
-        <v>276.0576</v>
+        <v>279.344</v>
       </c>
       <c r="G86">
         <v>20.5</v>
@@ -8321,37 +8321,37 @@
         <v>11.3</v>
       </c>
       <c r="M86">
-        <v>65.09438208</v>
+        <v>65.8693152</v>
       </c>
       <c r="N86">
-        <v>-53.79438208000001</v>
+        <v>-54.56931520000001</v>
       </c>
       <c r="O86">
-        <v>-12.9106516992</v>
+        <v>-13.096635648</v>
       </c>
       <c r="P86">
-        <v>-40.8837303808</v>
+        <v>-41.472679552</v>
       </c>
       <c r="Q86">
-        <v>-36.8837303808</v>
+        <v>-37.472679552</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.41609329030783</v>
+        <v>0.4407795096616854</v>
       </c>
       <c r="T86">
-        <v>6.243676845932497</v>
+        <v>6.659921968994664</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04166258152150509</v>
+        <v>0.04117243350360503</v>
       </c>
       <c r="W86">
-        <v>0.2259759632772291</v>
+        <v>0.2260915401798499</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1735940896729378</v>
+        <v>0.1715518062650209</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2582947356021252</v>
+        <v>0.2601947356021252</v>
       </c>
       <c r="C87">
-        <v>-169.8476932339802</v>
+        <v>-173.9227925571261</v>
       </c>
       <c r="D87">
-        <v>88.99630676601977</v>
+        <v>88.20760744287388</v>
       </c>
       <c r="E87">
-        <v>276.604</v>
+        <v>279.8904</v>
       </c>
       <c r="F87">
-        <v>279.344</v>
+        <v>282.6304</v>
       </c>
       <c r="G87">
         <v>20.5</v>
@@ -8403,37 +8403,37 @@
         <v>11.3</v>
       </c>
       <c r="M87">
-        <v>65.8693152</v>
+        <v>66.64424832</v>
       </c>
       <c r="N87">
-        <v>-54.56931520000001</v>
+        <v>-55.34424832000001</v>
       </c>
       <c r="O87">
-        <v>-13.096635648</v>
+        <v>-13.2826195968</v>
       </c>
       <c r="P87">
-        <v>-41.472679552</v>
+        <v>-42.0616287232</v>
       </c>
       <c r="Q87">
-        <v>-37.472679552</v>
+        <v>-38.0616287232</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4407795096616854</v>
+        <v>0.4689923317803771</v>
       </c>
       <c r="T87">
-        <v>6.659921968994664</v>
+        <v>7.13563068106571</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04117243350360503</v>
+        <v>0.04069368427681892</v>
       </c>
       <c r="W87">
-        <v>0.2260915401798499</v>
+        <v>0.2262044292475261</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1715518062650209</v>
+        <v>0.1695570178200788</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2601947356021252</v>
+        <v>0.2620947356021253</v>
       </c>
       <c r="C88">
-        <v>-173.9227925571261</v>
+        <v>-177.9840355216343</v>
       </c>
       <c r="D88">
-        <v>88.20760744287388</v>
+        <v>87.43276447836571</v>
       </c>
       <c r="E88">
-        <v>279.8904</v>
+        <v>283.1768</v>
       </c>
       <c r="F88">
-        <v>282.6304</v>
+        <v>285.9168</v>
       </c>
       <c r="G88">
         <v>20.5</v>
@@ -8485,37 +8485,37 @@
         <v>11.3</v>
       </c>
       <c r="M88">
-        <v>66.64424832</v>
+        <v>67.41918143999999</v>
       </c>
       <c r="N88">
-        <v>-55.34424832000001</v>
+        <v>-56.11918143999999</v>
       </c>
       <c r="O88">
-        <v>-13.2826195968</v>
+        <v>-13.4686035456</v>
       </c>
       <c r="P88">
-        <v>-42.0616287232</v>
+        <v>-42.65057789439999</v>
       </c>
       <c r="Q88">
-        <v>-38.0616287232</v>
+        <v>-38.65057789439999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4689923317803771</v>
+        <v>0.5015455880711753</v>
       </c>
       <c r="T88">
-        <v>7.13563068106571</v>
+        <v>7.684525348839996</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04069368427681892</v>
+        <v>0.04022594077938423</v>
       </c>
       <c r="W88">
-        <v>0.2262044292475261</v>
+        <v>0.2263147231642212</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1695570178200788</v>
+        <v>0.1676080865807675</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2620947356021253</v>
+        <v>0.2639947356021253</v>
       </c>
       <c r="C89">
-        <v>-177.9840355216343</v>
+        <v>-182.0317841034434</v>
       </c>
       <c r="D89">
-        <v>87.43276447836571</v>
+        <v>86.67141589655658</v>
       </c>
       <c r="E89">
-        <v>283.1768</v>
+        <v>286.4632</v>
       </c>
       <c r="F89">
-        <v>285.9168</v>
+        <v>289.2032</v>
       </c>
       <c r="G89">
         <v>20.5</v>
@@ -8567,37 +8567,37 @@
         <v>11.3</v>
       </c>
       <c r="M89">
-        <v>67.41918143999999</v>
+        <v>68.19411456</v>
       </c>
       <c r="N89">
-        <v>-56.11918143999999</v>
+        <v>-56.89411456000001</v>
       </c>
       <c r="O89">
-        <v>-13.4686035456</v>
+        <v>-13.6545874944</v>
       </c>
       <c r="P89">
-        <v>-42.65057789439999</v>
+        <v>-43.2395270656</v>
       </c>
       <c r="Q89">
-        <v>-38.65057789439999</v>
+        <v>-39.2395270656</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5015455880711753</v>
+        <v>0.5395243870771067</v>
       </c>
       <c r="T89">
-        <v>7.684525348839996</v>
+        <v>8.32490246124333</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04022594077938423</v>
+        <v>0.03976882781598213</v>
       </c>
       <c r="W89">
-        <v>0.2263147231642212</v>
+        <v>0.2264225104009914</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1676080865807675</v>
+        <v>0.1657034492332589</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2639947356021253</v>
+        <v>0.2658947356021252</v>
       </c>
       <c r="C90">
-        <v>-182.0317841034434</v>
+        <v>-186.0663877792512</v>
       </c>
       <c r="D90">
-        <v>86.67141589655658</v>
+        <v>85.92321222074878</v>
       </c>
       <c r="E90">
-        <v>286.4632</v>
+        <v>289.7496</v>
       </c>
       <c r="F90">
-        <v>289.2032</v>
+        <v>292.4896</v>
       </c>
       <c r="G90">
         <v>20.5</v>
@@ -8649,37 +8649,37 @@
         <v>11.3</v>
       </c>
       <c r="M90">
-        <v>68.19411456</v>
+        <v>68.96904768</v>
       </c>
       <c r="N90">
-        <v>-56.89411456000001</v>
+        <v>-57.66904768000001</v>
       </c>
       <c r="O90">
-        <v>-13.6545874944</v>
+        <v>-13.8405714432</v>
       </c>
       <c r="P90">
-        <v>-43.2395270656</v>
+        <v>-43.82847623680001</v>
       </c>
       <c r="Q90">
-        <v>-39.2395270656</v>
+        <v>-39.82847623680001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5395243870771067</v>
+        <v>0.5844084222659345</v>
       </c>
       <c r="T90">
-        <v>8.32490246124333</v>
+        <v>9.081711775901814</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03976882781598213</v>
+        <v>0.0393219870540048</v>
       </c>
       <c r="W90">
-        <v>0.2264225104009914</v>
+        <v>0.2265278754526657</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1657034492332589</v>
+        <v>0.16384161272502</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2658947356021252</v>
+        <v>0.2677947356021252</v>
       </c>
       <c r="C91">
-        <v>-186.0663877792512</v>
+        <v>-190.0881840614046</v>
       </c>
       <c r="D91">
-        <v>85.92321222074878</v>
+        <v>85.18781593859541</v>
       </c>
       <c r="E91">
-        <v>289.7496</v>
+        <v>293.036</v>
       </c>
       <c r="F91">
-        <v>292.4896</v>
+        <v>295.776</v>
       </c>
       <c r="G91">
         <v>20.5</v>
@@ -8731,37 +8731,37 @@
         <v>11.3</v>
       </c>
       <c r="M91">
-        <v>68.96904768</v>
+        <v>69.7439808</v>
       </c>
       <c r="N91">
-        <v>-57.66904768000001</v>
+        <v>-58.44398080000001</v>
       </c>
       <c r="O91">
-        <v>-13.8405714432</v>
+        <v>-14.026555392</v>
       </c>
       <c r="P91">
-        <v>-43.82847623680001</v>
+        <v>-44.41742540800001</v>
       </c>
       <c r="Q91">
-        <v>-39.82847623680001</v>
+        <v>-40.41742540800001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5844084222659345</v>
+        <v>0.6382692644925281</v>
       </c>
       <c r="T91">
-        <v>9.081711775901814</v>
+        <v>9.989882953491998</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0393219870540048</v>
+        <v>0.03888507608673808</v>
       </c>
       <c r="W91">
-        <v>0.2265278754526657</v>
+        <v>0.2266308990587472</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.16384161272502</v>
+        <v>0.1620211503614086</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2677947356021252</v>
+        <v>0.2696947356021252</v>
       </c>
       <c r="C92">
-        <v>-190.0881840614046</v>
+        <v>-194.0974990055548</v>
       </c>
       <c r="D92">
-        <v>85.18781593859541</v>
+        <v>84.46490099444523</v>
       </c>
       <c r="E92">
-        <v>293.036</v>
+        <v>296.3224</v>
       </c>
       <c r="F92">
-        <v>295.776</v>
+        <v>299.0624</v>
       </c>
       <c r="G92">
         <v>20.5</v>
@@ -8813,37 +8813,37 @@
         <v>11.3</v>
       </c>
       <c r="M92">
-        <v>69.7439808</v>
+        <v>70.51891392</v>
       </c>
       <c r="N92">
-        <v>-58.44398080000001</v>
+        <v>-59.21891392000001</v>
       </c>
       <c r="O92">
-        <v>-14.026555392</v>
+        <v>-14.2125393408</v>
       </c>
       <c r="P92">
-        <v>-44.41742540800001</v>
+        <v>-45.00637457920001</v>
       </c>
       <c r="Q92">
-        <v>-40.41742540800001</v>
+        <v>-41.00637457920001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6382692644925281</v>
+        <v>0.7040991827694757</v>
       </c>
       <c r="T92">
-        <v>9.989882953491998</v>
+        <v>11.09986994832444</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03888507608673808</v>
+        <v>0.03845776755831239</v>
       </c>
       <c r="W92">
-        <v>0.2266308990587472</v>
+        <v>0.2267316584097499</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1620211503614086</v>
+        <v>0.1602406981596349</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2696947356021252</v>
+        <v>0.2715947356021253</v>
       </c>
       <c r="C93">
-        <v>-194.0974990055548</v>
+        <v>-198.094647692682</v>
       </c>
       <c r="D93">
-        <v>84.46490099444523</v>
+        <v>83.75415230731799</v>
       </c>
       <c r="E93">
-        <v>296.3224</v>
+        <v>299.6088</v>
       </c>
       <c r="F93">
-        <v>299.0624</v>
+        <v>302.3488</v>
       </c>
       <c r="G93">
         <v>20.5</v>
@@ -8895,37 +8895,37 @@
         <v>11.3</v>
       </c>
       <c r="M93">
-        <v>70.51891392</v>
+        <v>71.29384704</v>
       </c>
       <c r="N93">
-        <v>-59.21891392000001</v>
+        <v>-59.99384704000001</v>
       </c>
       <c r="O93">
-        <v>-14.2125393408</v>
+        <v>-14.3985232896</v>
       </c>
       <c r="P93">
-        <v>-45.00637457920001</v>
+        <v>-45.59532375040001</v>
       </c>
       <c r="Q93">
-        <v>-41.00637457920001</v>
+        <v>-41.59532375040001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7040991827694757</v>
+        <v>0.7863865806156605</v>
       </c>
       <c r="T93">
-        <v>11.09986994832444</v>
+        <v>12.487353691865</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03845776755831239</v>
+        <v>0.03803974834572204</v>
       </c>
       <c r="W93">
-        <v>0.2267316584097499</v>
+        <v>0.2268302273400788</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1602406981596349</v>
+        <v>0.1584989514405084</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2715947356021253</v>
+        <v>0.2734947356021253</v>
       </c>
       <c r="C94">
-        <v>-198.094647692682</v>
+        <v>-202.0799346869864</v>
       </c>
       <c r="D94">
-        <v>83.75415230731799</v>
+        <v>83.05526531301359</v>
       </c>
       <c r="E94">
-        <v>299.6088</v>
+        <v>302.8952</v>
       </c>
       <c r="F94">
-        <v>302.3488</v>
+        <v>305.6352</v>
       </c>
       <c r="G94">
         <v>20.5</v>
@@ -8977,37 +8977,37 @@
         <v>11.3</v>
       </c>
       <c r="M94">
-        <v>71.29384704</v>
+        <v>72.06878016</v>
       </c>
       <c r="N94">
-        <v>-59.99384704000001</v>
+        <v>-60.76878016000001</v>
       </c>
       <c r="O94">
-        <v>-14.3985232896</v>
+        <v>-14.5845072384</v>
       </c>
       <c r="P94">
-        <v>-45.59532375040001</v>
+        <v>-46.18427292160001</v>
       </c>
       <c r="Q94">
-        <v>-41.59532375040001</v>
+        <v>-42.18427292160001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7863865806156605</v>
+        <v>0.8921846635607549</v>
       </c>
       <c r="T94">
-        <v>12.487353691865</v>
+        <v>14.27126136213143</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03803974834572204</v>
+        <v>0.0376307187936175</v>
       </c>
       <c r="W94">
-        <v>0.2268302273400788</v>
+        <v>0.226926676508465</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1584989514405084</v>
+        <v>0.1567946616400728</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2734947356021253</v>
+        <v>0.2753947356021252</v>
       </c>
       <c r="C95">
-        <v>-202.0799346869864</v>
+        <v>-206.0536544710436</v>
       </c>
       <c r="D95">
-        <v>83.05526531301359</v>
+        <v>82.3679455289564</v>
       </c>
       <c r="E95">
-        <v>302.8952</v>
+        <v>306.1816</v>
       </c>
       <c r="F95">
-        <v>305.6352</v>
+        <v>308.9216</v>
       </c>
       <c r="G95">
         <v>20.5</v>
@@ -9059,37 +9059,37 @@
         <v>11.3</v>
       </c>
       <c r="M95">
-        <v>72.06878016</v>
+        <v>72.84371328</v>
       </c>
       <c r="N95">
-        <v>-60.76878016000001</v>
+        <v>-61.54371328000001</v>
       </c>
       <c r="O95">
-        <v>-14.5845072384</v>
+        <v>-14.7704911872</v>
       </c>
       <c r="P95">
-        <v>-46.18427292160001</v>
+        <v>-46.7732220928</v>
       </c>
       <c r="Q95">
-        <v>-42.18427292160001</v>
+        <v>-42.7732220928</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8921846635607549</v>
+        <v>1.033248774154214</v>
       </c>
       <c r="T95">
-        <v>14.27126136213143</v>
+        <v>16.64980492248667</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0376307187936175</v>
+        <v>0.03723039199794072</v>
       </c>
       <c r="W95">
-        <v>0.226926676508465</v>
+        <v>0.2270210735668856</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1567946616400728</v>
+        <v>0.155126633324753</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2753947356021252</v>
+        <v>0.2772947356021253</v>
       </c>
       <c r="C96">
-        <v>-206.0536544710436</v>
+        <v>-210.0160918595309</v>
       </c>
       <c r="D96">
-        <v>82.3679455289564</v>
+        <v>81.6919081404691</v>
       </c>
       <c r="E96">
-        <v>306.1816</v>
+        <v>309.468</v>
       </c>
       <c r="F96">
-        <v>308.9216</v>
+        <v>312.208</v>
       </c>
       <c r="G96">
         <v>20.5</v>
@@ -9141,37 +9141,37 @@
         <v>11.3</v>
       </c>
       <c r="M96">
-        <v>72.84371328</v>
+        <v>73.6186464</v>
       </c>
       <c r="N96">
-        <v>-61.54371328000001</v>
+        <v>-62.31864640000001</v>
       </c>
       <c r="O96">
-        <v>-14.7704911872</v>
+        <v>-14.956475136</v>
       </c>
       <c r="P96">
-        <v>-46.7732220928</v>
+        <v>-47.362171264</v>
       </c>
       <c r="Q96">
-        <v>-42.7732220928</v>
+        <v>-43.362171264</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.033248774154214</v>
+        <v>1.230738528985058</v>
       </c>
       <c r="T96">
-        <v>16.64980492248667</v>
+        <v>19.97976590698402</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03723039199794072</v>
+        <v>0.03683849313480449</v>
       </c>
       <c r="W96">
-        <v>0.2270210735668856</v>
+        <v>0.2271134833188131</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.155126633324753</v>
+        <v>0.1534937213950187</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2772947356021253</v>
+        <v>0.2791947356021253</v>
       </c>
       <c r="C97">
-        <v>-210.0160918595309</v>
+        <v>-213.9675223927452</v>
       </c>
       <c r="D97">
-        <v>81.6919081404691</v>
+        <v>81.02687760725479</v>
       </c>
       <c r="E97">
-        <v>309.468</v>
+        <v>312.7544</v>
       </c>
       <c r="F97">
-        <v>312.208</v>
+        <v>315.4944</v>
       </c>
       <c r="G97">
         <v>20.5</v>
@@ -9223,37 +9223,37 @@
         <v>11.3</v>
       </c>
       <c r="M97">
-        <v>73.6186464</v>
+        <v>74.39357952</v>
       </c>
       <c r="N97">
-        <v>-62.31864640000001</v>
+        <v>-63.09357952000001</v>
       </c>
       <c r="O97">
-        <v>-14.956475136</v>
+        <v>-15.1424590848</v>
       </c>
       <c r="P97">
-        <v>-47.362171264</v>
+        <v>-47.9511204352</v>
       </c>
       <c r="Q97">
-        <v>-43.362171264</v>
+        <v>-43.9511204352</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.230738528985058</v>
+        <v>1.526973161231323</v>
       </c>
       <c r="T97">
-        <v>19.97976590698402</v>
+        <v>24.97470738373003</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03683849313480449</v>
+        <v>0.03645475883131695</v>
       </c>
       <c r="W97">
-        <v>0.2271134833188131</v>
+        <v>0.2272039678675755</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1534937213950187</v>
+        <v>0.1518948284638206</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2791947356021253</v>
+        <v>0.2810947356021252</v>
       </c>
       <c r="C98">
-        <v>-213.9675223927452</v>
+        <v>-217.9082127110552</v>
       </c>
       <c r="D98">
-        <v>81.02687760725479</v>
+        <v>80.3725872889448</v>
       </c>
       <c r="E98">
-        <v>312.7544</v>
+        <v>316.0408</v>
       </c>
       <c r="F98">
-        <v>315.4944</v>
+        <v>318.7808</v>
       </c>
       <c r="G98">
         <v>20.5</v>
@@ -9305,37 +9305,37 @@
         <v>11.3</v>
       </c>
       <c r="M98">
-        <v>74.39357952</v>
+        <v>75.16851264</v>
       </c>
       <c r="N98">
-        <v>-63.09357952000001</v>
+        <v>-63.86851264000001</v>
       </c>
       <c r="O98">
-        <v>-15.1424590848</v>
+        <v>-15.3284430336</v>
       </c>
       <c r="P98">
-        <v>-47.9511204352</v>
+        <v>-48.5400696064</v>
       </c>
       <c r="Q98">
-        <v>-43.9511204352</v>
+        <v>-44.5400696064</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.526973161231319</v>
+        <v>2.020697548308425</v>
       </c>
       <c r="T98">
-        <v>24.97470738372997</v>
+        <v>33.29960984497329</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03645475883131695</v>
+        <v>0.03607893657532399</v>
       </c>
       <c r="W98">
-        <v>0.2272039678675755</v>
+        <v>0.2272925867555386</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1518948284638206</v>
+        <v>0.1503289023971832</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2810947356021252</v>
+        <v>0.2829947356021253</v>
       </c>
       <c r="C99">
-        <v>-217.9082127110552</v>
+        <v>-221.8384209113567</v>
       </c>
       <c r="D99">
-        <v>80.3725872889448</v>
+        <v>79.72877908864326</v>
       </c>
       <c r="E99">
-        <v>316.0408</v>
+        <v>319.3271999999999</v>
       </c>
       <c r="F99">
-        <v>318.7808</v>
+        <v>322.0672</v>
       </c>
       <c r="G99">
         <v>20.5</v>
@@ -9387,37 +9387,37 @@
         <v>11.3</v>
       </c>
       <c r="M99">
-        <v>75.16851264</v>
+        <v>75.94344575999999</v>
       </c>
       <c r="N99">
-        <v>-63.86851264000001</v>
+        <v>-64.64344575999999</v>
       </c>
       <c r="O99">
-        <v>-15.3284430336</v>
+        <v>-15.5144269824</v>
       </c>
       <c r="P99">
-        <v>-48.5400696064</v>
+        <v>-49.1290187776</v>
       </c>
       <c r="Q99">
-        <v>-44.5400696064</v>
+        <v>-45.1290187776</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.020697548308425</v>
+        <v>3.008146322462638</v>
       </c>
       <c r="T99">
-        <v>33.29960984497329</v>
+        <v>49.94941476745994</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03607893657532399</v>
+        <v>0.03571078416129008</v>
       </c>
       <c r="W99">
-        <v>0.2272925867555386</v>
+        <v>0.2273793970947678</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1503289023971832</v>
+        <v>0.1487949340053754</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2829947356021253</v>
+        <v>0.2848947356021252</v>
       </c>
       <c r="C100">
-        <v>-221.8384209113567</v>
+        <v>-225.7583968865321</v>
       </c>
       <c r="D100">
-        <v>79.72877908864326</v>
+        <v>79.09520311346787</v>
       </c>
       <c r="E100">
-        <v>319.3271999999999</v>
+        <v>322.6136</v>
       </c>
       <c r="F100">
-        <v>322.0672</v>
+        <v>325.3536</v>
       </c>
       <c r="G100">
         <v>20.5</v>
@@ -9469,37 +9469,37 @@
         <v>11.3</v>
       </c>
       <c r="M100">
-        <v>75.94344575999999</v>
+        <v>76.71837888</v>
       </c>
       <c r="N100">
-        <v>-64.64344575999999</v>
+        <v>-65.41837888000001</v>
       </c>
       <c r="O100">
-        <v>-15.5144269824</v>
+        <v>-15.7004109312</v>
       </c>
       <c r="P100">
-        <v>-49.1290187776</v>
+        <v>-49.71796794880001</v>
       </c>
       <c r="Q100">
-        <v>-45.1290187776</v>
+        <v>-45.71796794880001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.008146322462638</v>
+        <v>5.970492644925276</v>
       </c>
       <c r="T100">
-        <v>49.94941476745994</v>
+        <v>99.89882953491988</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03571078416129008</v>
+        <v>0.0353500691697619</v>
       </c>
       <c r="W100">
-        <v>0.2273793970947678</v>
+        <v>0.2274644536897701</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1487949340053754</v>
+        <v>0.1472919548740078</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2848947356021252</v>
-      </c>
-      <c r="C101">
-        <v>-225.7583968865321</v>
-      </c>
-      <c r="D101">
-        <v>79.09520311346787</v>
-      </c>
-      <c r="E101">
-        <v>322.6136</v>
-      </c>
-      <c r="F101">
-        <v>325.3536</v>
-      </c>
-      <c r="G101">
-        <v>20.5</v>
-      </c>
-      <c r="H101">
-        <v>325.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15.3</v>
-      </c>
-      <c r="K101">
-        <v>4</v>
-      </c>
-      <c r="L101">
-        <v>11.3</v>
-      </c>
-      <c r="M101">
-        <v>76.71837888</v>
-      </c>
-      <c r="N101">
-        <v>-65.41837888000001</v>
-      </c>
-      <c r="O101">
-        <v>-15.7004109312</v>
-      </c>
-      <c r="P101">
-        <v>-49.71796794880001</v>
-      </c>
-      <c r="Q101">
-        <v>-45.71796794880001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.970492644925276</v>
-      </c>
-      <c r="T101">
-        <v>99.89882953491988</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0353500691697619</v>
-      </c>
-      <c r="W101">
-        <v>0.2274644536897701</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1472919548740078</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
